--- a/outputs/results/12a/results_12a_final.xlsx
+++ b/outputs/results/12a/results_12a_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="all_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -554,48 +564,24 @@
       <c r="G2" t="n">
         <v>0.6382792115128209</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
         <v>2.227087997341149e-06</v>
       </c>
-      <c r="I2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -625,48 +611,24 @@
       <c r="G3" t="n">
         <v>0.639204</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,48 +658,24 @@
       <c r="G4" t="n">
         <v>0.6343255043029785</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>0.0007247853209264576</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,48 +705,24 @@
       <c r="G5" t="n">
         <v>0.6080413644562611</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
         <v>0.009696280344509325</v>
       </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8108108108108109</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1229166666666667</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,48 +752,24 @@
       <c r="G6" t="n">
         <v>0.64</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -909,48 +799,24 @@
       <c r="G7" t="n">
         <v>0.6399903431451417</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>1.441656627305284e-06</v>
       </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -981,46 +847,52 @@
         <v>0.223293979127919</v>
       </c>
       <c r="H8" t="n">
+        <v>2.227087997341149e-06</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.2014106733770808</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1052,46 +924,52 @@
         <v>0.3761944036855912</v>
       </c>
       <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.04570979684019617</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1114,54 +992,60 @@
         <v>2009</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7319402405360937</v>
+        <v>0.7149657089019512</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3580358922481537</v>
+        <v>0.4297910034656525</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00820888951420784</v>
+        <v>0.0007247853209264576</v>
       </c>
       <c r="I10" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.02312231808900833</v>
+      </c>
+      <c r="K10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>8</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.8</v>
       </c>
-      <c r="N10" t="n">
-        <v>1</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.68</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.1777777777777778</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.08888888888888889</v>
       </c>
     </row>
@@ -1185,54 +1069,60 @@
         <v>2009</v>
       </c>
       <c r="E11" t="n">
-        <v>0.486111111111111</v>
+        <v>0.4791666666666666</v>
       </c>
       <c r="F11" t="n">
-        <v>0.609264137130985</v>
+        <v>0.6049238593532071</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2741606954812124</v>
+        <v>0.2738984661880489</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3886823637074523</v>
+        <v>0.009696280344509325</v>
       </c>
       <c r="I11" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3883814896124541</v>
+      </c>
+      <c r="K11" t="n">
         <v>16</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>9</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0.64</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
         <v>0.64</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1268,42 +1158,48 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>16</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.64</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
         <v>0.64</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1327,55 +1223,61 @@
         <v>2009</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6527777777777779</v>
+        <v>0.6597222222222223</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7912109815802271</v>
+        <v>0.7302182906962319</v>
       </c>
       <c r="G13" t="n">
-        <v>0.473175400123597</v>
+        <v>0.4981815520498338</v>
       </c>
       <c r="H13" t="n">
-        <v>6.283065748490748e-08</v>
+        <v>1.441656627305284e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>6.335829577909895e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
-        <v>0.8205128205128205</v>
-      </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="R13" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.5555555555555556</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.72</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.1555555555555556</v>
-      </c>
       <c r="U13" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.2541666666666667</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.2111111111111111</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1680555555555556</v>
       </c>
     </row>
     <row r="14">
@@ -1407,46 +1309,52 @@
         <v>0.4144737581190095</v>
       </c>
       <c r="H14" t="n">
+        <v>0.2014106733770808</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J14" t="n">
         <v>0.7833577863639724</v>
       </c>
-      <c r="I14" t="n">
-        <v>9</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
-      </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6428571428571429</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="15">
@@ -1478,46 +1386,52 @@
         <v>0.2545735890098271</v>
       </c>
       <c r="H15" t="n">
+        <v>0.04570979684019617</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.3137136777324644</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1454,61 @@
         <v>2010</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4466666666666667</v>
+        <v>0.4533333333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>0.379942123094297</v>
+        <v>0.3845656530095889</v>
       </c>
       <c r="G16" t="n">
-        <v>0.306172251701355</v>
+        <v>0.2784052491188049</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1123559102416039</v>
+        <v>0.02312231808900833</v>
       </c>
       <c r="I16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.3041164577007294</v>
+      </c>
+      <c r="K16" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1531,61 @@
         <v>2010</v>
       </c>
       <c r="E17" t="n">
-        <v>0.52</v>
+        <v>0.5266666666666666</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4808495670995671</v>
+        <v>0.4850162337662337</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4480604958059615</v>
+        <v>0.4466774947482055</v>
       </c>
       <c r="H17" t="n">
-        <v>1.584038067466776e-12</v>
+        <v>0.3883814896124541</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>1.247681410993825e-12</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>0.625</v>
+        <v>9</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="R17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.52</v>
       </c>
-      <c r="S17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.16</v>
-      </c>
       <c r="U17" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.7600000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.8300000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1691,46 +1617,52 @@
         <v>0.388621494554386</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J18" t="n">
         <v>0.7879234167893957</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -1753,55 +1685,61 @@
         <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4866666666666666</v>
+        <v>0.5133333333333334</v>
       </c>
       <c r="F19" t="n">
-        <v>0.459244071146245</v>
+        <v>0.428546176046176</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3514883211898782</v>
+        <v>0.4046306477662753</v>
       </c>
       <c r="H19" t="n">
-        <v>7.724365950953985e-08</v>
+        <v>6.335829577909895e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J19" t="n">
-        <v>14</v>
+        <v>1.032617660339527e-08</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5882352941176471</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5625</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="R19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="T19" t="n">
         <v>0.44</v>
       </c>
-      <c r="S19" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.1866666666666667</v>
-      </c>
       <c r="U19" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.1766666666666667</v>
       </c>
     </row>
     <row r="20">
@@ -1833,46 +1771,52 @@
         <v>0.2170654818769425</v>
       </c>
       <c r="H20" t="n">
+        <v>0.7833577863639724</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J20" t="n">
         <v>0.4083412920571219</v>
       </c>
-      <c r="I20" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" t="n">
-        <v>6</v>
-      </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="S20" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1904,45 +1848,51 @@
         <v>0.2148953671258025</v>
       </c>
       <c r="H21" t="n">
+        <v>0.3137136777324644</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J21" t="n">
         <v>0.3182923340208793</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>7</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="L21" t="n">
+      <c r="N21" t="n">
         <v>13</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.7</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.8</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.25</v>
       </c>
-      <c r="T21" t="n">
+      <c r="V21" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="U21" t="n">
+      <c r="W21" t="n">
         <v>0.2833333333333333</v>
       </c>
     </row>
@@ -1966,55 +1916,61 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6822619047619047</v>
+        <v>0.7056593406593407</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2379890829324722</v>
+        <v>0.1864664405584335</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09450928121805191</v>
+        <v>0.3041164577007294</v>
       </c>
       <c r="I22" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.380422979593277</v>
+      </c>
+      <c r="K22" t="n">
+        <v>9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
       <c r="O22" t="n">
-        <v>0.625</v>
+        <v>0.75</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="R22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T22" t="n">
         <v>0.76</v>
       </c>
-      <c r="S22" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.08000000000000002</v>
-      </c>
       <c r="U22" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.17</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.1233333333333334</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6126984126984126</v>
+        <v>0.7354653679653679</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2549496525175192</v>
+        <v>0.3590262769149449</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1290546634897831</v>
+        <v>1.247681410993825e-12</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>3.761922345160043e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R23" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.26</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24</v>
+        <v>0.44</v>
       </c>
       <c r="U23" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="24">
@@ -2117,46 +2079,52 @@
         <v>0.3877373884297521</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.7879234167893957</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5714285714285714</v>
+        <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.7333333333333334</v>
       </c>
     </row>
     <row r="25">
@@ -2179,55 +2147,61 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7083241758241758</v>
+        <v>0.701231867547657</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2719960540167289</v>
+        <v>0.1925736914123412</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03962087894369956</v>
+        <v>1.032617660339527e-08</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>0.2800529722350836</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6956521739130435</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.2266666666666667</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.2133333333333333</v>
+      <c r="W25" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -2259,46 +2233,52 @@
         <v>0.1956060252987059</v>
       </c>
       <c r="H26" t="n">
+        <v>0.4083412920571219</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J26" t="n">
         <v>0.5851407395184636</v>
       </c>
-      <c r="I26" t="n">
-        <v>7</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3</v>
-      </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.2</v>
       </c>
-      <c r="R26" t="n">
-        <v>0.76</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.68</v>
       </c>
       <c r="U26" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
@@ -2330,46 +2310,52 @@
         <v>0.1639718747066577</v>
       </c>
       <c r="H27" t="n">
+        <v>0.3182923340208793</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J27" t="n">
         <v>0.5415036188475644</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
+        <v>9</v>
+      </c>
+      <c r="L27" t="n">
         <v>6</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
       <c r="M27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
+        <v>9</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q27" t="n">
         <v>0.6</v>
       </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S27" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T27" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="U27" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.13</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2012</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8732874968169085</v>
+        <v>0.8250171998624011</v>
       </c>
       <c r="G28" t="n">
-        <v>0.155405193567276</v>
+        <v>0.1645167320966721</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6614319682121277</v>
+        <v>0.380422979593277</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.6059996485710144</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R28" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S28" t="n">
-        <v>0.21</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T28" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="U28" t="n">
         <v>0.24</v>
       </c>
-      <c r="U28" t="n">
-        <v>0.27</v>
+      <c r="V28" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.84</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8352453102453102</v>
+        <v>0.7870021645021645</v>
       </c>
       <c r="G29" t="n">
-        <v>0.166953586544577</v>
+        <v>0.163493155064301</v>
       </c>
       <c r="H29" t="n">
-        <v>0.654490273882216</v>
+        <v>3.761922345160043e-05</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>0.3276797576208203</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L29" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7619047619047619</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>6</v>
       </c>
       <c r="O29" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="P29" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V29" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0.2</v>
+      <c r="W29" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="30">
@@ -2543,45 +2541,51 @@
         <v>0.2226751315721354</v>
       </c>
       <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
         <v>0.1696014828544953</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8955542986425339</v>
+        <v>0.8563492063492063</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1465093221462065</v>
+        <v>0.1589590198350416</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1188784941635189</v>
+        <v>0.2800529722350836</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.4010896844925375</v>
+      </c>
+      <c r="K31" t="n">
+        <v>9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>7</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="n">
         <v>8</v>
       </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>13</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.8</v>
-      </c>
       <c r="O31" t="n">
-        <v>0.8</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P31" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="R31" t="n">
-        <v>0.84</v>
+        <v>0.1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.18</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.21</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.1366666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -2684,48 +2694,24 @@
       <c r="G32" t="n">
         <v>0.6397517261347714</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>1.163216072620251e-07</v>
       </c>
-      <c r="I32" t="n">
-        <v>16</v>
-      </c>
-      <c r="J32" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2755,48 +2741,24 @@
       <c r="G33" t="n">
         <v>0.64</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>9</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2826,48 +2788,24 @@
       <c r="G34" t="n">
         <v>0.633694589138031</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
         <v>0.004945225547999144</v>
       </c>
-      <c r="I34" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2897,48 +2835,24 @@
       <c r="G35" t="n">
         <v>0.5970282271938142</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
         <v>0.01037416278161608</v>
       </c>
-      <c r="I35" t="n">
-        <v>16</v>
-      </c>
-      <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2968,48 +2882,24 @@
       <c r="G36" t="n">
         <v>0.64</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>16</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3039,48 +2929,24 @@
       <c r="G37" t="n">
         <v>0.6399850529731999</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>16</v>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3111,46 +2977,52 @@
         <v>0.6399149582541784</v>
       </c>
       <c r="H38" t="n">
+        <v>1.163216072620251e-07</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J38" t="n">
         <v>5.774910310799749e-07</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>16</v>
       </c>
-      <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R38" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
@@ -3185,42 +3057,48 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>16</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>9</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0.64</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>0.64</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.3</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.2</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3253,46 +3131,52 @@
         <v>0.6338368058204651</v>
       </c>
       <c r="H40" t="n">
+        <v>0.004945225547999144</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.004833243321627378</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>16</v>
       </c>
-      <c r="J40" t="n">
+      <c r="N40" t="n">
         <v>9</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
       <c r="O40" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="41">
@@ -3324,46 +3208,52 @@
         <v>0.6164883184918493</v>
       </c>
       <c r="H41" t="n">
+        <v>0.01037416278161608</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J41" t="n">
         <v>0.001678897141775105</v>
       </c>
-      <c r="I41" t="n">
-        <v>16</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7804878048780488</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
-        <v>0.64</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R41" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="S41" t="n">
-        <v>0.3</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1</v>
+        <v>0.5166666666666666</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.5111111111111112</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.5055555555555555</v>
       </c>
     </row>
     <row r="42">
@@ -3398,42 +3288,48 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>16</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>9</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.64</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>0.64</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.3</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.2</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3466,46 +3362,52 @@
         <v>0.6398924456781397</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J43" t="n">
         <v>1.447725522269862e-11</v>
       </c>
-      <c r="I43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0.75</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2104166666666666</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1611111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1118055555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
@@ -3537,46 +3439,52 @@
         <v>0.3997083474543894</v>
       </c>
       <c r="H44" t="n">
+        <v>5.774910310799749e-07</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J44" t="n">
         <v>9.269796436416404e-06</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>10</v>
       </c>
-      <c r="J44" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
@@ -3611,42 +3519,48 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>15</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.4</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
       <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.4</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.2</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3679,46 +3593,52 @@
         <v>0.3964213132858276</v>
       </c>
       <c r="H46" t="n">
+        <v>0.004833243321627378</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.004498659633100033</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="n">
+      <c r="N46" t="n">
         <v>15</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
       <c r="O46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U46" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
@@ -3750,46 +3670,52 @@
         <v>0.3992378639494475</v>
       </c>
       <c r="H47" t="n">
+        <v>0.001678897141775105</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J47" t="n">
         <v>0.0003971452859503358</v>
       </c>
-      <c r="I47" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>6</v>
-      </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
         <v>9</v>
       </c>
-      <c r="M47" t="n">
-        <v>0.6086956521739131</v>
-      </c>
       <c r="N47" t="n">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="P47" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R47" t="n">
-        <v>0.64</v>
+        <v>0.9</v>
       </c>
       <c r="S47" t="n">
-        <v>0.33</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T47" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U47" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.67</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.7466666666666667</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.8233333333333334</v>
       </c>
     </row>
     <row r="48">
@@ -3824,42 +3750,48 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>15</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0.4</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>0.4</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.3</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>0.2</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3892,46 +3824,52 @@
         <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.447725522269862e-11</v>
       </c>
       <c r="I49" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
         <v>10</v>
       </c>
-      <c r="J49" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.5714285714285714</v>
-      </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.3</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T49" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9066666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -3963,46 +3901,52 @@
         <v>0.2171061075379025</v>
       </c>
       <c r="H50" t="n">
+        <v>9.269796436416404e-06</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J50" t="n">
         <v>0.4888998500171703</v>
       </c>
-      <c r="I50" t="n">
-        <v>5</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -4034,46 +3978,52 @@
         <v>0.2633358424813289</v>
       </c>
       <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J51" t="n">
         <v>0.06085160778335204</v>
       </c>
-      <c r="I51" t="n">
-        <v>9</v>
-      </c>
-      <c r="J51" t="n">
-        <v>8</v>
-      </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4046,61 @@
         <v>2011</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7201984126984127</v>
+        <v>0.7269404125286478</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2852432727813721</v>
+        <v>0.2754010558128357</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01487493608146906</v>
+        <v>0.004498659633100033</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>0.004524882417172194</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="T52" t="n">
         <v>0.72</v>
       </c>
-      <c r="N52" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0.16</v>
-      </c>
       <c r="U52" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.09333333333333334</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.04666666666666667</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4123,61 @@
         <v>2011</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8210081585081584</v>
+        <v>0.8267401960784313</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2202869608750037</v>
+        <v>0.1883966684161324</v>
       </c>
       <c r="H53" t="n">
-        <v>1.713269544996963e-05</v>
+        <v>0.0003971452859503358</v>
       </c>
       <c r="I53" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6659912562313409</v>
+      </c>
+      <c r="K53" t="n">
         <v>10</v>
       </c>
-      <c r="J53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
         <v>0.625</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.4</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R53" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.12</v>
+        <v>0.8</v>
       </c>
       <c r="T53" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W53" t="n">
         <v>0.08000000000000002</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0.04000000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -4250,42 +4212,48 @@
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>10</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>15</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0.4</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
         <v>0.4</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>0.2</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4309,55 +4277,61 @@
         <v>2011</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.84</v>
       </c>
       <c r="F55" t="n">
-        <v>0.780877684407096</v>
+        <v>0.8133241758241758</v>
       </c>
       <c r="G55" t="n">
-        <v>0.282606541385438</v>
+        <v>0.2797455037100474</v>
       </c>
       <c r="H55" t="n">
-        <v>5.530121171447283e-07</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J55" t="n">
+        <v>5.454768206519132e-07</v>
+      </c>
+      <c r="K55" t="n">
         <v>10</v>
       </c>
-      <c r="J55" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U55" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
@@ -4389,46 +4363,52 @@
         <v>0.24675586501407</v>
       </c>
       <c r="H56" t="n">
+        <v>0.4888998500171703</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J56" t="n">
         <v>0.4980951475015878</v>
       </c>
-      <c r="I56" t="n">
-        <v>7</v>
-      </c>
-      <c r="J56" t="n">
-        <v>2</v>
-      </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7368421052631579</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U56" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.2833333333333333</v>
+      <c r="V56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="57">
@@ -4460,46 +4440,52 @@
         <v>0.1772604300135964</v>
       </c>
       <c r="H57" t="n">
+        <v>0.06085160778335204</v>
+      </c>
+      <c r="I57" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J57" t="n">
         <v>0.4668391189611855</v>
       </c>
-      <c r="I57" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L57" t="n">
         <v>14</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7058823529411765</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P57" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R57" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.3</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T57" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.44</v>
       </c>
       <c r="U57" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.28</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="58">
@@ -4522,55 +4508,61 @@
         <v>2012</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7933333333333334</v>
+        <v>0.8066666666666668</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7715509928667823</v>
+        <v>0.7694472194472194</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1959438323974609</v>
+        <v>0.1930386424064636</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4696164429187775</v>
+        <v>0.004524882417172194</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0.08967553079128265</v>
       </c>
       <c r="K58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7058823529411765</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0.06666666666666667</v>
-      </c>
       <c r="R58" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U58" t="n">
         <v>0.3</v>
       </c>
-      <c r="T58" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="U58" t="n">
-        <v>0.3666666666666667</v>
+      <c r="V58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="59">
@@ -4593,55 +4585,61 @@
         <v>2012</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9133333333333333</v>
+        <v>0.8866666666666667</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9025641025641025</v>
+        <v>0.8702686202686202</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1423480244754639</v>
+        <v>0.1594322370126732</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6407988137251898</v>
+        <v>0.6659912562313409</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.03996660532733744</v>
       </c>
       <c r="K59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>4</v>
+      </c>
+      <c r="N59" t="n">
         <v>15</v>
       </c>
-      <c r="M59" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="P59" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="S59" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>0.24</v>
+        <v>0.84</v>
       </c>
       <c r="U59" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.3200000000000001</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.36</v>
       </c>
     </row>
     <row r="60">
@@ -4676,42 +4674,48 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>10</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>15</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0.4</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
       <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>0.4</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>0.3</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>0.2</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4735,55 +4739,61 @@
         <v>2012</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8168440617353662</v>
+        <v>0.7897294372294372</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2222609874122116</v>
+        <v>0.2436442160491342</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01329423575621427</v>
+        <v>5.454768206519132e-07</v>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>0.1179448659596483</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L61" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W61" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.1066666666666667</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.1033333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -4829,7 +4839,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.696</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="4">
@@ -4849,7 +4859,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.615</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="6">
@@ -4869,7 +4879,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
     </row>
   </sheetData>
@@ -4948,22 +4958,22 @@
         <v>0.514</v>
       </c>
       <c r="D2" t="n">
-        <v>0.658</v>
+        <v>0.552</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.499</v>
+        <v>0.485</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.987</v>
+        <v>0.783</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="3">
@@ -4978,25 +4988,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.71</v>
       </c>
       <c r="D3" t="n">
-        <v>0.741</v>
+        <v>0.657</v>
       </c>
       <c r="E3" t="n">
-        <v>0.92</v>
+        <v>0.919</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639</v>
+        <v>0.527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08</v>
+        <v>0.081</v>
       </c>
       <c r="H3" t="n">
-        <v>0.613</v>
+        <v>0.722</v>
       </c>
       <c r="I3" t="n">
-        <v>0.187</v>
+        <v>0.209</v>
       </c>
     </row>
     <row r="4">
@@ -5014,22 +5024,22 @@
         <v>0.621</v>
       </c>
       <c r="D4" t="n">
-        <v>0.718</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>0.725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.616</v>
+        <v>0.653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.618</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -5044,25 +5054,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.628</v>
       </c>
       <c r="D5" t="n">
-        <v>0.729</v>
+        <v>0.539</v>
       </c>
       <c r="E5" t="n">
-        <v>0.908</v>
+        <v>0.75</v>
       </c>
       <c r="F5" t="n">
-        <v>0.622</v>
+        <v>0.452</v>
       </c>
       <c r="G5" t="n">
-        <v>0.092</v>
+        <v>0.25</v>
       </c>
       <c r="H5" t="n">
-        <v>0.613</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.197</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="6">
@@ -5080,22 +5090,22 @@
         <v>0.625</v>
       </c>
       <c r="D6" t="n">
-        <v>0.738</v>
+        <v>0.702</v>
       </c>
       <c r="E6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.708</v>
+        <v>0.604</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="I6" t="n">
-        <v>0.225</v>
+        <v>0.207</v>
       </c>
     </row>
     <row r="7">
@@ -5110,25 +5120,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
       <c r="D7" t="n">
-        <v>0.752</v>
+        <v>0.704</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="F7" t="n">
-        <v>0.67</v>
+        <v>0.581</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06</v>
+        <v>0.075</v>
       </c>
       <c r="H7" t="n">
-        <v>0.644</v>
+        <v>0.639</v>
       </c>
       <c r="I7" t="n">
-        <v>0.177</v>
+        <v>0.188</v>
       </c>
     </row>
   </sheetData>
@@ -5184,7 +5194,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="4">
@@ -5204,7 +5214,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.628</v>
       </c>
     </row>
     <row r="6">
@@ -5224,7 +5234,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="8">
@@ -5249,7 +5259,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.706</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="10">
@@ -5269,7 +5279,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.636</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="12">
@@ -5289,7 +5299,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.617</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12a/results_12a_final.xlsx
+++ b/outputs/results/12a/results_12a_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="all_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -554,48 +564,24 @@
       <c r="G2" t="n">
         <v>0.6382792115128209</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
         <v>2.227087997341149e-06</v>
       </c>
-      <c r="I2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -617,56 +603,32 @@
         <v>2008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.53125</v>
+        <v>0.5625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6625</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.639204</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
+        <v>0.63762</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,48 +658,24 @@
       <c r="G4" t="n">
         <v>0.6343255043029785</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>0.0007247853209264576</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,56 +697,32 @@
         <v>2008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6599885366826156</v>
+        <v>0.6200252218112126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6080413644562611</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.009696280344509325</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
+        <v>0.61169557758658</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8108108108108109</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1229166666666667</v>
-      </c>
+        <v>0.006415031715643183</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,48 +752,24 @@
       <c r="G6" t="n">
         <v>0.64</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -909,48 +799,24 @@
       <c r="G7" t="n">
         <v>0.6399903431451417</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>1.441656627305284e-06</v>
       </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -978,49 +844,55 @@
         <v>0.7895733600717869</v>
       </c>
       <c r="G8" t="n">
-        <v>0.223293979127919</v>
+        <v>0.223303826104632</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2014106733770808</v>
+        <v>2.227087997341149e-06</v>
       </c>
       <c r="I8" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2013580998841109</v>
+      </c>
+      <c r="K8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +915,61 @@
         <v>2009</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F9" t="n">
-        <v>0.730835362280964</v>
+        <v>0.7408809088396684</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3761944036855912</v>
+        <v>0.3894544746082663</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04570979684019617</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.06756790404391019</v>
+      </c>
+      <c r="K9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +992,61 @@
         <v>2009</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.5972222222222222</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7319402405360937</v>
+        <v>0.7682975470199734</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3580358922481537</v>
+        <v>0.4124722182750702</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00820888951420784</v>
+        <v>0.0007247853209264576</v>
       </c>
       <c r="I10" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.02146328799426556</v>
+      </c>
+      <c r="K10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1069,61 @@
         <v>2009</v>
       </c>
       <c r="E11" t="n">
-        <v>0.486111111111111</v>
+        <v>0.7013888888888888</v>
       </c>
       <c r="F11" t="n">
-        <v>0.609264137130985</v>
+        <v>0.7841629414080072</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2741606954812124</v>
+        <v>0.4221149937586579</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3886823637074523</v>
+        <v>0.006415031715643183</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>0.03524554605091722</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7804878048780488</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>0.64</v>
+        <v>0.7647058823529411</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.8125</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="R11" t="n">
-        <v>0.64</v>
+        <v>0.1875</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.2979166666666666</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2611111111111111</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.2243055555555556</v>
       </c>
     </row>
     <row r="12">
@@ -1256,54 +1146,60 @@
         <v>2009</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3125</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6925</v>
+        <v>0.6433522727272727</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5736267796116965</v>
+        <v>0.597905722679953</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>16</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.64</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
         <v>0.64</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1327,55 +1223,61 @@
         <v>2009</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6527777777777779</v>
+        <v>0.6041666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7912109815802271</v>
+        <v>0.7277563822365023</v>
       </c>
       <c r="G13" t="n">
-        <v>0.473175400123597</v>
+        <v>0.5277682624628074</v>
       </c>
       <c r="H13" t="n">
-        <v>6.283065748490748e-08</v>
+        <v>1.441656627305284e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>6.870550982506571e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8205128205128205</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="R13" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.72</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.1555555555555556</v>
-      </c>
       <c r="U13" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.24375</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1229166666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1404,49 +1306,55 @@
         <v>0.4843657067570111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4144737581190095</v>
+        <v>0.414458315320779</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7833577863639724</v>
+        <v>0.2013580998841109</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>0.7831513448365189</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6428571428571429</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1377,61 @@
         <v>2010</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.3666666666666668</v>
       </c>
       <c r="F15" t="n">
-        <v>0.382668172470804</v>
+        <v>0.3432342403898131</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2545735890098271</v>
+        <v>0.2691364155907441</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3137136777324644</v>
+        <v>0.06756790404391019</v>
       </c>
       <c r="I15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2335397944770118</v>
+      </c>
+      <c r="K15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -1540,54 +1454,60 @@
         <v>2010</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4466666666666667</v>
+        <v>0.4866666666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>0.379942123094297</v>
+        <v>0.4074754901960784</v>
       </c>
       <c r="G16" t="n">
-        <v>0.306172251701355</v>
+        <v>0.297024130821228</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1123559102416039</v>
+        <v>0.02146328799426556</v>
       </c>
       <c r="I16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1030884981155396</v>
+      </c>
+      <c r="K16" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>14</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>0.44</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.28</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.1866666666666667</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.09333333333333334</v>
       </c>
     </row>
@@ -1611,55 +1531,61 @@
         <v>2010</v>
       </c>
       <c r="E17" t="n">
-        <v>0.52</v>
+        <v>0.4866666666666667</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4808495670995671</v>
+        <v>0.4006410411054374</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4480604958059615</v>
+        <v>0.4509714523981775</v>
       </c>
       <c r="H17" t="n">
-        <v>1.584038067466776e-12</v>
+        <v>0.03524554605091722</v>
       </c>
       <c r="I17" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.345329283715288e-09</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="n">
         <v>10</v>
       </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
       <c r="O17" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.8</v>
       </c>
-      <c r="R17" t="n">
-        <v>0.52</v>
-      </c>
       <c r="S17" t="n">
-        <v>0.24</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T17" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.7066666666666668</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.7533333333333334</v>
       </c>
     </row>
     <row r="18">
@@ -1682,55 +1608,61 @@
         <v>2010</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.388621494554386</v>
+        <v>0.286243122480371</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7879234167893957</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5310173697270469</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -1753,54 +1685,60 @@
         <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4866666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.459244071146245</v>
+        <v>0.4350231203788211</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3514883211898782</v>
+        <v>0.3799678171789461</v>
       </c>
       <c r="H19" t="n">
-        <v>7.724365950953985e-08</v>
+        <v>6.870550982506571e-06</v>
       </c>
       <c r="I19" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0003125164049146888</v>
+      </c>
+      <c r="K19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>14</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.44</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.28</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>0.1866666666666667</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>0.09333333333333334</v>
       </c>
     </row>
@@ -1830,49 +1768,55 @@
         <v>0.5675036075036075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2170654818769425</v>
+        <v>0.2166228214605736</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4083412920571219</v>
+        <v>0.7831513448365189</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>0.4096710720916179</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="S20" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1895,55 +1839,61 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.76</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7107798481711525</v>
+        <v>0.7180061115355233</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2148953671258025</v>
+        <v>0.2050999311524101</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3182923340208793</v>
+        <v>0.2335397944770118</v>
       </c>
       <c r="I21" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1703114877878713</v>
+      </c>
+      <c r="K21" t="n">
         <v>7</v>
       </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="L21" t="n">
-        <v>13</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7368421052631579</v>
-      </c>
       <c r="N21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P21" t="n">
         <v>0.7</v>
       </c>
-      <c r="O21" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.8</v>
-      </c>
       <c r="S21" t="n">
-        <v>0.25</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.29</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.2966666666666667</v>
       </c>
     </row>
     <row r="22">
@@ -1966,55 +1916,61 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.74</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6822619047619047</v>
+        <v>0.6653113063407181</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2379890829324722</v>
+        <v>0.3036090731620789</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09450928121805191</v>
+        <v>0.1030884981155396</v>
       </c>
       <c r="I22" t="n">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="J22" t="n">
+        <v>0.04995658993721008</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M22" t="n">
         <v>6</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7692307692307693</v>
-      </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O22" t="n">
-        <v>0.625</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0.6</v>
       </c>
       <c r="S22" t="n">
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.64</v>
       </c>
       <c r="U22" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.48</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.76</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6126984126984126</v>
+        <v>0.7452044513457557</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2549496525175192</v>
+        <v>0.1937083563388475</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1290546634897831</v>
+        <v>6.345329283715288e-09</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>0.4122335526638031</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -2108,55 +2070,61 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4533333333333334</v>
+        <v>0.4299999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3877373884297521</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.5310173697270469</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5714285714285714</v>
+        <v>7</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4</v>
+        <v>0.375</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1</v>
+        <v>0.5499999999999999</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.65</v>
       </c>
     </row>
     <row r="25">
@@ -2179,55 +2147,61 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.78</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7083241758241758</v>
+        <v>0.6697619047619047</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2719960540167289</v>
+        <v>0.1911018202226515</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03962087894369956</v>
+        <v>0.0003125164049146888</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>0.3535185571767958</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6956521739130435</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.2266666666666667</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.2133333333333333</v>
+      <c r="W25" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -2256,49 +2230,55 @@
         <v>0.7565384615384615</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1956060252987059</v>
+        <v>0.1952257532119012</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5851407395184636</v>
+        <v>0.4096710720916179</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0.5807833091234721</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.2</v>
       </c>
-      <c r="R26" t="n">
-        <v>0.76</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.68</v>
       </c>
       <c r="U26" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8391575091575091</v>
+        <v>0.8046607997265891</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1639718747066577</v>
+        <v>0.1711757218822195</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5415036188475644</v>
+        <v>0.1703114877878713</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.2445929608881404</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6</v>
+        <v>7</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="R27" t="n">
-        <v>0.84</v>
+        <v>0.1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.28</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="U27" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -2395,52 +2381,58 @@
         <v>0.8533333333333334</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8732874968169085</v>
+        <v>0.8705357142857143</v>
       </c>
       <c r="G28" t="n">
-        <v>0.155405193567276</v>
+        <v>0.1734478324651718</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6614319682121277</v>
+        <v>0.04995658993721008</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.7832706570625305</v>
       </c>
       <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>12</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>3</v>
       </c>
-      <c r="L28" t="n">
-        <v>15</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.625</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R28" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.21</v>
+        <v>0.8</v>
       </c>
       <c r="T28" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="U28" t="n">
         <v>0.24</v>
       </c>
-      <c r="U28" t="n">
-        <v>0.27</v>
+      <c r="V28" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.84</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8352453102453102</v>
+        <v>0.8508910533910534</v>
       </c>
       <c r="G29" t="n">
-        <v>0.166953586544577</v>
+        <v>0.1593602437535897</v>
       </c>
       <c r="H29" t="n">
-        <v>0.654490273882216</v>
+        <v>0.4122335526638031</v>
       </c>
       <c r="I29" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.6606583851526479</v>
+      </c>
+      <c r="K29" t="n">
         <v>8</v>
       </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="n">
-        <v>12</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.7619047619047619</v>
-      </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>11</v>
       </c>
       <c r="O29" t="n">
         <v>0.7272727272727273</v>
       </c>
       <c r="P29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R29" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.8</v>
-      </c>
       <c r="S29" t="n">
-        <v>0.2</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2</v>
+        <v>0.76</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.2133333333333334</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6383333333333334</v>
+        <v>0.6689393939393939</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2226751315721354</v>
+        <v>0.209706699861893</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1696014828544953</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5062240663900414</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.88</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8955542986425339</v>
+        <v>0.8633333333333333</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1465093221462065</v>
+        <v>0.1773794384353292</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1188784941635189</v>
+        <v>0.3535185571767958</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J31" t="n">
+        <v>0.1045056959598985</v>
+      </c>
+      <c r="K31" t="n">
+        <v>6</v>
+      </c>
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" t="n">
         <v>13</v>
       </c>
-      <c r="M31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.8</v>
-      </c>
       <c r="O31" t="n">
-        <v>0.8</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P31" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="Q31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S31" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="R31" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.18</v>
-      </c>
       <c r="T31" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.32</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="32">
@@ -2684,48 +2694,24 @@
       <c r="G32" t="n">
         <v>0.6397517261347714</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>1.163216072620251e-07</v>
       </c>
-      <c r="I32" t="n">
-        <v>16</v>
-      </c>
-      <c r="J32" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2747,56 +2733,32 @@
         <v>2008</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F33" t="n">
         <v>0.64</v>
       </c>
       <c r="G33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16</v>
-      </c>
+        <v>0.640004</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>9</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2826,48 +2788,24 @@
       <c r="G34" t="n">
         <v>0.633694589138031</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
         <v>0.004945225547999144</v>
       </c>
-      <c r="I34" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2889,56 +2827,32 @@
         <v>2008</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4375</v>
+        <v>0.4027777777777778</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6099316826272843</v>
+        <v>0.5935431786350904</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5970282271938142</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.01037416278161608</v>
-      </c>
-      <c r="I35" t="n">
-        <v>16</v>
-      </c>
+        <v>0.602424413989084</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.008022271582238406</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2968,48 +2882,24 @@
       <c r="G36" t="n">
         <v>0.64</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>16</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3039,48 +2929,24 @@
       <c r="G37" t="n">
         <v>0.6399850529731999</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>16</v>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3111,46 +2977,52 @@
         <v>0.6399149582541784</v>
       </c>
       <c r="H38" t="n">
+        <v>1.163216072620251e-07</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J38" t="n">
         <v>5.774910310799749e-07</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>16</v>
       </c>
-      <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R38" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
@@ -3173,54 +3045,60 @@
         <v>2009</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4409722222222222</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6120833333333334</v>
+        <v>0.64</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6361520000000001</v>
+        <v>0.640004</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>16</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>9</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0.64</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>0.64</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.3</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.2</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3253,46 +3131,52 @@
         <v>0.6338368058204651</v>
       </c>
       <c r="H40" t="n">
+        <v>0.004945225547999144</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.004833243321627378</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>16</v>
       </c>
-      <c r="J40" t="n">
+      <c r="N40" t="n">
         <v>9</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
       <c r="O40" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3199,61 @@
         <v>2009</v>
       </c>
       <c r="E41" t="n">
+        <v>0.3680555555555556</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5715171920470833</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.6197384399241023</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.008022271582238406</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.00189478638605586</v>
+      </c>
+      <c r="K41" t="n">
+        <v>10</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R41" t="n">
         <v>0.375</v>
       </c>
-      <c r="F41" t="n">
-        <v>0.5702398439866471</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.6164883184918493</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.001678897141775105</v>
-      </c>
-      <c r="I41" t="n">
-        <v>16</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.64</v>
-      </c>
       <c r="S41" t="n">
-        <v>0.3</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1</v>
+        <v>0.4291666666666666</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.4111111111111111</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.3930555555555556</v>
       </c>
     </row>
     <row r="42">
@@ -3398,42 +3288,48 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>16</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>9</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.64</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>0.64</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.3</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.2</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3466,46 +3362,52 @@
         <v>0.6398924456781397</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J43" t="n">
         <v>1.447725522269862e-11</v>
       </c>
-      <c r="I43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0.75</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2104166666666666</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1611111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1118055555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
@@ -3537,46 +3439,52 @@
         <v>0.3997083474543894</v>
       </c>
       <c r="H44" t="n">
+        <v>5.774910310799749e-07</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J44" t="n">
         <v>9.269796436416404e-06</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>10</v>
       </c>
-      <c r="J44" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
@@ -3599,54 +3507,60 @@
         <v>2010</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="F45" t="n">
         <v>0.4</v>
       </c>
       <c r="G45" t="n">
+        <v>0.400004</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" t="n">
+        <v>15</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.4</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" t="n">
-        <v>15</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.4</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.2</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3679,46 +3593,52 @@
         <v>0.3964213132858276</v>
       </c>
       <c r="H46" t="n">
+        <v>0.004833243321627378</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.004498659633100033</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="n">
+      <c r="N46" t="n">
         <v>15</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
       <c r="O46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U46" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
@@ -3741,55 +3661,61 @@
         <v>2010</v>
       </c>
       <c r="E47" t="n">
-        <v>0.6</v>
+        <v>0.6599999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4867383107088989</v>
+        <v>0.5300668337510444</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3992378639494475</v>
+        <v>0.396994335420163</v>
       </c>
       <c r="H47" t="n">
-        <v>0.0003971452859503358</v>
+        <v>0.00189478638605586</v>
       </c>
       <c r="I47" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.000944072558993784</v>
+      </c>
+      <c r="K47" t="n">
         <v>7</v>
       </c>
-      <c r="J47" t="n">
-        <v>6</v>
-      </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" t="n">
         <v>3</v>
       </c>
-      <c r="L47" t="n">
-        <v>9</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.6086956521739131</v>
-      </c>
       <c r="N47" t="n">
+        <v>10</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="P47" t="n">
         <v>0.7</v>
       </c>
-      <c r="O47" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="P47" t="n">
+      <c r="Q47" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="R47" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.64</v>
-      </c>
       <c r="S47" t="n">
-        <v>0.33</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T47" t="n">
-        <v>0.32</v>
+        <v>0.68</v>
       </c>
       <c r="U47" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.3033333333333333</v>
       </c>
     </row>
     <row r="48">
@@ -3824,42 +3750,48 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>15</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0.4</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>0.4</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.3</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>0.2</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3892,46 +3824,52 @@
         <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.447725522269862e-11</v>
       </c>
       <c r="I49" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
         <v>10</v>
       </c>
-      <c r="J49" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.5714285714285714</v>
-      </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.3</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T49" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9066666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -3954,55 +3892,61 @@
         <v>2011</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6866666666666666</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7188704177323103</v>
+        <v>0.7121560027519779</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2171061075379025</v>
+        <v>0.2018854667325396</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4888998500171703</v>
+        <v>9.269796436416404e-06</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>2010</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0.2836981690820184</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +3969,61 @@
         <v>2011</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.66</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6406762192056309</v>
+        <v>0.6379456216298321</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2633358424813289</v>
+        <v>0.275546070995502</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06085160778335204</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>0.09994717136335954</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4046,61 @@
         <v>2011</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7201984126984127</v>
+        <v>0.6490277777777778</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2852432727813721</v>
+        <v>0.2956588268280029</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01487493608146906</v>
+        <v>0.004498659633100033</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>0.04527655243873596</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M52" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
         <v>0.4</v>
       </c>
       <c r="R52" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.19</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U52" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4123,61 @@
         <v>2011</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8210081585081584</v>
+        <v>0.7448354341736695</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2202869608750037</v>
+        <v>0.1992076201484164</v>
       </c>
       <c r="H53" t="n">
-        <v>1.713269544996963e-05</v>
+        <v>0.000944072558993784</v>
       </c>
       <c r="I53" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.3125768383210795</v>
+      </c>
+      <c r="K53" t="n">
         <v>10</v>
       </c>
-      <c r="J53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U53" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="54">
@@ -4238,54 +4200,60 @@
         <v>2011</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4533333333333334</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3350785506919857</v>
+        <v>0.3548833409373044</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>10</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>15</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0.4</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
         <v>0.4</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>0.2</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4309,55 +4277,61 @@
         <v>2011</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="F55" t="n">
-        <v>0.780877684407096</v>
+        <v>0.8217560217560217</v>
       </c>
       <c r="G55" t="n">
-        <v>0.282606541385438</v>
+        <v>0.2985668730255759</v>
       </c>
       <c r="H55" t="n">
-        <v>5.530121171447283e-07</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1.730361613813838e-05</v>
+      </c>
+      <c r="K55" t="n">
         <v>10</v>
       </c>
-      <c r="J55" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U55" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
@@ -4380,55 +4354,61 @@
         <v>2012</v>
       </c>
       <c r="E56" t="n">
-        <v>0.82</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8052686202686202</v>
+        <v>0.7991558441558442</v>
       </c>
       <c r="G56" t="n">
-        <v>0.24675586501407</v>
+        <v>0.2115804651756399</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4980951475015878</v>
+        <v>0.2836981690820184</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>0.4658564190194761</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7368421052631579</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U56" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R56" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="U56" t="n">
-        <v>0.2833333333333333</v>
+      <c r="V56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="57">
@@ -4451,55 +4431,61 @@
         <v>2012</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.84</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7988220551378445</v>
+        <v>0.8150140056022409</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1772604300135964</v>
+        <v>0.1701000564539752</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4668391189611855</v>
+        <v>0.09994717136335954</v>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.1714323171251515</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7058823529411765</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.625</v>
       </c>
       <c r="P57" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>0.8</v>
       </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
       <c r="T57" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.52</v>
       </c>
       <c r="U57" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="58">
@@ -4522,55 +4508,61 @@
         <v>2012</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7933333333333334</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7715509928667823</v>
+        <v>0.7919822282980177</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1959438323974609</v>
+        <v>0.1846328228712082</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4696164429187775</v>
+        <v>0.04527655243873596</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0.1825455874204636</v>
       </c>
       <c r="K58" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7058823529411765</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.625</v>
       </c>
       <c r="P58" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
         <v>0.8</v>
       </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
       <c r="T58" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.52</v>
       </c>
       <c r="U58" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="59">
@@ -4593,55 +4585,61 @@
         <v>2012</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9133333333333333</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9025641025641025</v>
+        <v>0.8263736263736262</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1423480244754639</v>
+        <v>0.1805536222732456</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6407988137251898</v>
+        <v>0.3125768383210795</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.4174607803528357</v>
       </c>
       <c r="K59" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L59" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="M59" t="n">
-        <v>0.8235294117647058</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P59" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R59" t="n">
-        <v>0.88</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.21</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T59" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="U59" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="60">
@@ -4664,54 +4662,60 @@
         <v>2012</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5966666666666667</v>
+        <v>0.5766666666666667</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5267948717948717</v>
+        <v>0.5151587301587301</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3160468795061819</v>
+        <v>0.348215617519158</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>10</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>15</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0.4</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
       <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>0.4</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>0.3</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>0.2</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4735,55 +4739,61 @@
         <v>2012</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8266666666666668</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8168440617353662</v>
+        <v>0.8208333333333332</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2222609874122116</v>
+        <v>0.2813524655943827</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01329423575621427</v>
+        <v>1.730361613813838e-05</v>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J61" t="n">
+        <v>0.0002678318549983173</v>
+      </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
+      <c r="L61" t="n">
+        <v>5</v>
+      </c>
+      <c r="M61" t="n">
         <v>2</v>
       </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
-        <v>13</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.8571428571428571</v>
-      </c>
       <c r="N61" t="n">
-        <v>0.9</v>
+        <v>10</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="P61" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R61" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S61" t="n">
-        <v>0.11</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T61" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.24</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -4819,7 +4829,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.514</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="3">
@@ -4829,7 +4839,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.696</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -4849,7 +4859,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.615</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="6">
@@ -4859,7 +4869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.625</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="7">
@@ -4869,7 +4879,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.644</v>
+        <v>0.632</v>
       </c>
     </row>
   </sheetData>
@@ -4945,25 +4955,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.52</v>
       </c>
       <c r="D2" t="n">
-        <v>0.658</v>
+        <v>0.575</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.825</v>
       </c>
       <c r="F2" t="n">
-        <v>0.499</v>
+        <v>0.485</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.175</v>
       </c>
       <c r="H2" t="n">
-        <v>0.987</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -4978,25 +4988,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.741</v>
+        <v>0.659</v>
       </c>
       <c r="E3" t="n">
-        <v>0.92</v>
+        <v>0.884</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639</v>
+        <v>0.57</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="H3" t="n">
-        <v>0.613</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>0.187</v>
+        <v>0.229</v>
       </c>
     </row>
     <row r="4">
@@ -5014,22 +5024,22 @@
         <v>0.621</v>
       </c>
       <c r="D4" t="n">
-        <v>0.718</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>0.725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.616</v>
+        <v>0.653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.618</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -5044,25 +5054,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.656</v>
       </c>
       <c r="D5" t="n">
-        <v>0.729</v>
+        <v>0.575</v>
       </c>
       <c r="E5" t="n">
-        <v>0.908</v>
+        <v>0.703</v>
       </c>
       <c r="F5" t="n">
-        <v>0.622</v>
+        <v>0.519</v>
       </c>
       <c r="G5" t="n">
-        <v>0.092</v>
+        <v>0.297</v>
       </c>
       <c r="H5" t="n">
-        <v>0.613</v>
+        <v>0.539</v>
       </c>
       <c r="I5" t="n">
-        <v>0.197</v>
+        <v>0.345</v>
       </c>
     </row>
     <row r="6">
@@ -5077,25 +5087,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.612</v>
       </c>
       <c r="D6" t="n">
-        <v>0.738</v>
+        <v>0.671</v>
       </c>
       <c r="E6" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="F6" t="n">
-        <v>0.708</v>
+        <v>0.551</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="I6" t="n">
-        <v>0.225</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7">
@@ -5110,25 +5120,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.632</v>
       </c>
       <c r="D7" t="n">
-        <v>0.752</v>
+        <v>0.616</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="F7" t="n">
-        <v>0.67</v>
+        <v>0.521</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="H7" t="n">
-        <v>0.644</v>
+        <v>0.733</v>
       </c>
       <c r="I7" t="n">
-        <v>0.177</v>
+        <v>0.267</v>
       </c>
     </row>
   </sheetData>
@@ -5174,7 +5184,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="3">
@@ -5184,7 +5194,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.6929999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -5204,7 +5214,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.656</v>
       </c>
     </row>
     <row r="6">
@@ -5214,7 +5224,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="7">
@@ -5224,7 +5234,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="8">
@@ -5239,7 +5249,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.537</v>
+        <v>0.529</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5259,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.706</v>
+        <v>0.709</v>
       </c>
     </row>
     <row r="10">
@@ -5259,7 +5269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.51</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="11">
@@ -5269,7 +5279,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.636</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="12">
@@ -5279,7 +5289,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.584</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="13">
@@ -5289,7 +5299,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.611</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12a/results_12a_final.xlsx
+++ b/outputs/results/12a/results_12a_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="all_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -554,48 +564,24 @@
       <c r="G2" t="n">
         <v>0.6382792115128209</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
         <v>2.227087997341149e-06</v>
       </c>
-      <c r="I2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -617,56 +603,32 @@
         <v>2008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.53125</v>
+        <v>0.4791666666666666</v>
       </c>
       <c r="F3" t="n">
         <v>0.6625</v>
       </c>
       <c r="G3" t="n">
-        <v>0.639204</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
+        <v>0.63764</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,48 +658,24 @@
       <c r="G4" t="n">
         <v>0.6343255043029785</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>0.0007247853209264576</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,56 +697,32 @@
         <v>2008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6599885366826156</v>
+        <v>0.6677380788071579</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6080413644562611</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.009696280344509325</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
+        <v>0.6082803135393544</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8108108108108109</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1229166666666667</v>
-      </c>
+        <v>0.007099558765006013</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,48 +752,24 @@
       <c r="G6" t="n">
         <v>0.64</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -909,48 +799,24 @@
       <c r="G7" t="n">
         <v>0.6399903431451417</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>1.441656627305284e-06</v>
       </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -978,49 +844,55 @@
         <v>0.7895733600717869</v>
       </c>
       <c r="G8" t="n">
-        <v>0.223293979127919</v>
+        <v>0.2232575886833975</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2014106733770808</v>
+        <v>2.227087997341149e-06</v>
       </c>
       <c r="I8" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2010326509660355</v>
+      </c>
+      <c r="K8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +915,61 @@
         <v>2009</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="F9" t="n">
-        <v>0.730835362280964</v>
+        <v>0.7797901023937923</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3761944036855912</v>
+        <v>0.3384137293034424</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04570979684019617</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.05988531559711226</v>
+      </c>
+      <c r="K9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +992,61 @@
         <v>2009</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.5833333333333333</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7319402405360937</v>
+        <v>0.7272725124308657</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3580358922481537</v>
+        <v>0.4810805916786194</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00820888951420784</v>
+        <v>0.0007247853209264576</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J10" t="n">
+        <v>0.0007135643973015249</v>
+      </c>
+      <c r="K10" t="n">
+        <v>15</v>
+      </c>
+      <c r="L10" t="n">
         <v>8</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q10" t="n">
+        <v>0.6521739130434783</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="R10" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.2666666666666667</v>
-      </c>
       <c r="T10" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3104166666666667</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2277777777777778</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1451388888888889</v>
       </c>
     </row>
     <row r="11">
@@ -1185,54 +1069,60 @@
         <v>2009</v>
       </c>
       <c r="E11" t="n">
-        <v>0.486111111111111</v>
+        <v>0.2708333333333334</v>
       </c>
       <c r="F11" t="n">
-        <v>0.609264137130985</v>
+        <v>0.5204007257530612</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2741606954812124</v>
+        <v>0.3151004520217146</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3886823637074523</v>
+        <v>0.007099558765006013</v>
       </c>
       <c r="I11" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2450224678250312</v>
+      </c>
+      <c r="K11" t="n">
         <v>16</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>9</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0.64</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
         <v>0.64</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.3</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.2</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1256,54 +1146,60 @@
         <v>2009</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3125</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6925</v>
+        <v>0.612391774891775</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5736267796116965</v>
+        <v>0.5487541689483905</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>16</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.64</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
         <v>0.64</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1327,55 +1223,61 @@
         <v>2009</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6527777777777779</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7912109815802271</v>
+        <v>0.7337196249420515</v>
       </c>
       <c r="G13" t="n">
-        <v>0.473175400123597</v>
+        <v>0.5469983050117696</v>
       </c>
       <c r="H13" t="n">
-        <v>6.283065748490748e-08</v>
+        <v>1.441656627305284e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>8.738439907445302e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
-        <v>0.8205128205128205</v>
-      </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0.72</v>
+        <v>0.125</v>
       </c>
       <c r="S13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="V13" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="T13" t="n">
-        <v>0.1555555555555556</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.07777777777777778</v>
+      <c r="W13" t="n">
+        <v>0.1791666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1404,49 +1306,55 @@
         <v>0.4843657067570111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4144737581190095</v>
+        <v>0.4144752054655376</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7833577863639724</v>
+        <v>0.2010326509660355</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>0.7833759333301835</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6428571428571429</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1377,61 @@
         <v>2010</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>0.382668172470804</v>
+        <v>0.3477440696558344</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2545735890098271</v>
+        <v>0.2576640641696799</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3137136777324644</v>
+        <v>0.05988531559711226</v>
       </c>
       <c r="I15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2790311006286889</v>
+      </c>
+      <c r="K15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1454,61 @@
         <v>2010</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4466666666666667</v>
+        <v>0.4866666666666666</v>
       </c>
       <c r="F16" t="n">
-        <v>0.379942123094297</v>
+        <v>0.3993687592600636</v>
       </c>
       <c r="G16" t="n">
-        <v>0.306172251701355</v>
+        <v>0.31248539686203</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1123559102416039</v>
+        <v>0.0007135643973015249</v>
       </c>
       <c r="I16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.05300547182559967</v>
+      </c>
+      <c r="K16" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1531,61 @@
         <v>2010</v>
       </c>
       <c r="E17" t="n">
-        <v>0.52</v>
+        <v>0.5133333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4808495670995671</v>
+        <v>0.4741829004329003</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4480604958059615</v>
+        <v>0.4291029897555166</v>
       </c>
       <c r="H17" t="n">
-        <v>1.584038067466776e-12</v>
+        <v>0.2450224678250312</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>1.307426591177734e-12</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>0.625</v>
+        <v>9</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="R17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.52</v>
       </c>
-      <c r="S17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.16</v>
-      </c>
       <c r="U17" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.7600000000000001</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.8300000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -1685,52 +1611,58 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.388621494554386</v>
+        <v>0.3742570728447315</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7879234167893957</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -1753,55 +1685,61 @@
         <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4866666666666666</v>
+        <v>0.4933333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>0.459244071146245</v>
+        <v>0.3971412411118294</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3514883211898782</v>
+        <v>0.4382886799469176</v>
       </c>
       <c r="H19" t="n">
-        <v>7.724365950953985e-08</v>
+        <v>8.738439907445302e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J19" t="n">
+        <v>0.001088453841364532</v>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="n">
         <v>14</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
       <c r="M19" t="n">
-        <v>0.5882352941176471</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q19" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.1833333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -1830,49 +1768,55 @@
         <v>0.5675036075036075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2170654818769425</v>
+        <v>0.2171170452416072</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4083412920571219</v>
+        <v>0.7833759333301835</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>0.408195950211893</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="S20" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1895,55 +1839,61 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7066666666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7107798481711525</v>
+        <v>0.6375</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2148953671258025</v>
+        <v>0.2139509992535819</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3182923340208793</v>
+        <v>0.2790311006286889</v>
       </c>
       <c r="I21" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3658785053189866</v>
+      </c>
+      <c r="K21" t="n">
         <v>7</v>
       </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="L21" t="n">
-        <v>13</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.7368421052631579</v>
-      </c>
       <c r="N21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P21" t="n">
         <v>0.7</v>
       </c>
-      <c r="O21" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.8</v>
-      </c>
       <c r="S21" t="n">
-        <v>0.25</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.29</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.2966666666666667</v>
       </c>
     </row>
     <row r="22">
@@ -1966,55 +1916,61 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6822619047619047</v>
+        <v>0.7039822595704949</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2379890829324722</v>
+        <v>0.1859025806188583</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09450928121805191</v>
+        <v>0.05300547182559967</v>
       </c>
       <c r="I22" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3051965832710266</v>
+      </c>
+      <c r="K22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>0.625</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.12</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="U22" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.08666666666666667</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.6866666666666666</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6126984126984126</v>
+        <v>0.6028894716394716</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2549496525175192</v>
+        <v>0.2347105509011065</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1290546634897831</v>
+        <v>1.307426591177734e-12</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>0.2229904208180457</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -2108,54 +2070,60 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4533333333333334</v>
+        <v>0.4733333333333333</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3877373884297521</v>
+        <v>0.3476433652623713</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
         <v>10</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>15</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
-      </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.4</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1</v>
-      </c>
       <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
         <v>0.4</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.3</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.2</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2179,55 +2147,61 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7083241758241758</v>
+        <v>0.7056593406593407</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2719960540167289</v>
+        <v>0.1906887768331494</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03962087894369956</v>
+        <v>0.001088453841364532</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>0.3299585131884852</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6956521739130435</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.2266666666666667</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.2133333333333333</v>
+      <c r="W25" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -2256,49 +2230,55 @@
         <v>0.7565384615384615</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1956060252987059</v>
+        <v>0.1952111422470758</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5851407395184636</v>
+        <v>0.408195950211893</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0.5805960860213302</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.2</v>
       </c>
-      <c r="R26" t="n">
-        <v>0.76</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.68</v>
       </c>
       <c r="U26" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8533333333333334</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8391575091575091</v>
+        <v>0.8303968253968254</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1639718747066577</v>
+        <v>0.1803668001541342</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5415036188475644</v>
+        <v>0.3658785053189866</v>
       </c>
       <c r="I27" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.3098591549295774</v>
+      </c>
+      <c r="K27" t="n">
         <v>6</v>
       </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="n">
         <v>4</v>
       </c>
-      <c r="L27" t="n">
-        <v>15</v>
-      </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
+        <v>13</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q27" t="n">
         <v>0.75</v>
       </c>
-      <c r="N27" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.28</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="U27" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2012</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.86</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8732874968169085</v>
+        <v>0.8640277777777777</v>
       </c>
       <c r="G28" t="n">
-        <v>0.155405193567276</v>
+        <v>0.1775731146335602</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6614319682121277</v>
+        <v>0.3051965832710266</v>
       </c>
       <c r="I28" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.6078245043754578</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8</v>
+      </c>
+      <c r="L28" t="n">
         <v>7</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>15</v>
-      </c>
       <c r="M28" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7</v>
+        <v>8</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="R28" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S28" t="n">
-        <v>0.21</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T28" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U28" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2266666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.84</v>
+        <v>0.7933333333333334</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8352453102453102</v>
+        <v>0.7805827067669173</v>
       </c>
       <c r="G29" t="n">
-        <v>0.166953586544577</v>
+        <v>0.1537400608477741</v>
       </c>
       <c r="H29" t="n">
-        <v>0.654490273882216</v>
+        <v>0.2229904208180457</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J29" t="n">
+        <v>0.1857078644858586</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
         <v>3</v>
       </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>12</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.7619047619047619</v>
-      </c>
       <c r="N29" t="n">
+        <v>13</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T29" t="n">
         <v>0.8</v>
       </c>
-      <c r="O29" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.2</v>
-      </c>
       <c r="U29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.2833333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -2543,45 +2541,51 @@
         <v>0.2226751315721354</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1696014828544953</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.1696014828544952</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8466666666666667</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8955542986425339</v>
+        <v>0.8046401259559154</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1465093221462065</v>
+        <v>0.1831110971507507</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1188784941635189</v>
+        <v>0.3299585131884852</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1279285809962587</v>
+      </c>
+      <c r="K31" t="n">
         <v>8</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>13</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>11</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.8</v>
       </c>
-      <c r="N31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.18</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.22</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2133333333333334</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -2684,48 +2694,24 @@
       <c r="G32" t="n">
         <v>0.6397517261347714</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>1.163216072620251e-07</v>
       </c>
-      <c r="I32" t="n">
-        <v>16</v>
-      </c>
-      <c r="J32" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2747,56 +2733,32 @@
         <v>2008</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.4756944444444444</v>
       </c>
       <c r="F33" t="n">
-        <v>0.64</v>
+        <v>0.63125</v>
       </c>
       <c r="G33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16</v>
-      </c>
+        <v>0.639208</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>9</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2826,48 +2788,24 @@
       <c r="G34" t="n">
         <v>0.633694589138031</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
         <v>0.004945225547999144</v>
       </c>
-      <c r="I34" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2889,56 +2827,32 @@
         <v>2008</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4375</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6099316826272843</v>
+        <v>0.6492392369627277</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5970282271938142</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.01037416278161608</v>
-      </c>
-      <c r="I35" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5974860277448919</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.00802711199299953</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2968,48 +2882,24 @@
       <c r="G36" t="n">
         <v>0.64</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>16</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3039,48 +2929,24 @@
       <c r="G37" t="n">
         <v>0.6399850529731999</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>16</v>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3111,46 +2977,52 @@
         <v>0.6399149582541784</v>
       </c>
       <c r="H38" t="n">
+        <v>1.163216072620251e-07</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J38" t="n">
         <v>5.774910310799749e-07</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>16</v>
       </c>
-      <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R38" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
@@ -3173,54 +3045,60 @@
         <v>2009</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4409722222222222</v>
+        <v>0.3298611111111112</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6120833333333334</v>
+        <v>0.6059375</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6361520000000001</v>
+        <v>0.63532</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>16</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>9</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0.64</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>0.64</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.3</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.2</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3253,46 +3131,52 @@
         <v>0.6338368058204651</v>
       </c>
       <c r="H40" t="n">
+        <v>0.004945225547999144</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.004833243321627378</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>16</v>
       </c>
-      <c r="J40" t="n">
+      <c r="N40" t="n">
         <v>9</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
       <c r="O40" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3199,61 @@
         <v>2009</v>
       </c>
       <c r="E41" t="n">
-        <v>0.375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5702398439866471</v>
+        <v>0.5903696824009323</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6164883184918493</v>
+        <v>0.626134719090174</v>
       </c>
       <c r="H41" t="n">
-        <v>0.001678897141775105</v>
+        <v>0.00802711199299953</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J41" t="n">
-        <v>9</v>
+        <v>0.0005685128011414496</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7804878048780488</v>
+        <v>8</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
-        <v>0.64</v>
+        <v>0.5517241379310345</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R41" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="S41" t="n">
-        <v>0.3</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1</v>
+        <v>0.5166666666666666</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.5111111111111112</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.5055555555555555</v>
       </c>
     </row>
     <row r="42">
@@ -3398,42 +3288,48 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>16</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>9</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.64</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>0.64</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.3</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.2</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3466,46 +3362,52 @@
         <v>0.6398924456781397</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J43" t="n">
         <v>1.447725522269862e-11</v>
       </c>
-      <c r="I43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0.75</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2104166666666666</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1611111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1118055555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
@@ -3537,46 +3439,52 @@
         <v>0.3997083474543894</v>
       </c>
       <c r="H44" t="n">
+        <v>5.774910310799749e-07</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J44" t="n">
         <v>9.269796436416404e-06</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>10</v>
       </c>
-      <c r="J44" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
@@ -3611,42 +3519,48 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>10</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>15</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.4</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
       <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.4</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.2</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3679,46 +3593,52 @@
         <v>0.3964213132858276</v>
       </c>
       <c r="H46" t="n">
+        <v>0.004833243321627378</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.004498659633100033</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="n">
+      <c r="N46" t="n">
         <v>15</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
       <c r="O46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U46" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
@@ -3741,55 +3661,61 @@
         <v>2010</v>
       </c>
       <c r="E47" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.4725133689839572</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.3993576965855991</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.0005685128011414496</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.000175670512838312</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>10</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F47" t="n">
-        <v>0.4867383107088989</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.3992378639494475</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.0003971452859503358</v>
-      </c>
-      <c r="I47" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>6</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3</v>
-      </c>
-      <c r="L47" t="n">
-        <v>9</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.6086956521739131</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.3</v>
-      </c>
       <c r="Q47" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="R47" t="n">
         <v>0.4</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.64</v>
       </c>
-      <c r="S47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.32</v>
-      </c>
       <c r="U47" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.3866666666666667</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.3933333333333334</v>
       </c>
     </row>
     <row r="48">
@@ -3824,42 +3750,48 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>15</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0.4</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>0.4</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.3</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>0.2</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3892,46 +3824,52 @@
         <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.447725522269862e-11</v>
       </c>
       <c r="I49" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
         <v>10</v>
       </c>
-      <c r="J49" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.5714285714285714</v>
-      </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.3</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T49" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9066666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -3960,49 +3898,55 @@
         <v>0.7188704177323103</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2171061075379025</v>
+        <v>0.2170978251558427</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4888998500171703</v>
+        <v>9.269796436416404e-06</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>2010</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0.4887805999806067</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +3969,61 @@
         <v>2011</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6406762192056309</v>
+        <v>0.6797654684496789</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2633358424813289</v>
+        <v>0.2510168120327554</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06085160778335204</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>0.1074787090317408</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4046,61 @@
         <v>2011</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7201984126984127</v>
+        <v>0.6658061821219715</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2852432727813721</v>
+        <v>0.2832237780094147</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01487493608146906</v>
+        <v>0.004498659633100033</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>0.01034864317625761</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M52" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.4</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R52" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.19</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="T52" t="n">
-        <v>0.16</v>
+        <v>0.44</v>
       </c>
       <c r="U52" t="n">
-        <v>0.13</v>
+        <v>0.28</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.09333333333333334</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4123,61 @@
         <v>2011</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.78</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8210081585081584</v>
+        <v>0.7670741758241757</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2202869608750037</v>
+        <v>0.2140749374199644</v>
       </c>
       <c r="H53" t="n">
-        <v>1.713269544996963e-05</v>
+        <v>0.000175670512838312</v>
       </c>
       <c r="I53" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.4135391445390953</v>
+      </c>
+      <c r="K53" t="n">
         <v>10</v>
       </c>
-      <c r="J53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U53" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="54">
@@ -4238,54 +4200,60 @@
         <v>2011</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4533333333333334</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3350785506919857</v>
+        <v>0.3548833409373043</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>10</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>15</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0.4</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
         <v>0.4</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>0.2</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4309,55 +4277,61 @@
         <v>2011</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.9266666666666667</v>
       </c>
       <c r="F55" t="n">
-        <v>0.780877684407096</v>
+        <v>0.8918650793650793</v>
       </c>
       <c r="G55" t="n">
-        <v>0.282606541385438</v>
+        <v>0.2814239160624182</v>
       </c>
       <c r="H55" t="n">
-        <v>5.530121171447283e-07</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J55" t="n">
+        <v>8.246480369543175e-06</v>
+      </c>
+      <c r="K55" t="n">
         <v>10</v>
       </c>
-      <c r="J55" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U55" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
@@ -4380,55 +4354,61 @@
         <v>2012</v>
       </c>
       <c r="E56" t="n">
-        <v>0.82</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8052686202686202</v>
+        <v>0.811060606060606</v>
       </c>
       <c r="G56" t="n">
-        <v>0.24675586501407</v>
+        <v>0.2291226429802088</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4980951475015878</v>
+        <v>0.4887805999806067</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J56" t="n">
+        <v>0.4822713321748682</v>
+      </c>
+      <c r="K56" t="n">
+        <v>6</v>
+      </c>
+      <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
+        <v>4</v>
+      </c>
+      <c r="N56" t="n">
         <v>13</v>
       </c>
-      <c r="M56" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O56" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P56" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q56" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S56" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="R56" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.25</v>
-      </c>
       <c r="T56" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="U56" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.32</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="57">
@@ -4451,55 +4431,61 @@
         <v>2012</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7988220551378445</v>
+        <v>0.8102182539682539</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1772604300135964</v>
+        <v>0.1738080189345715</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4668391189611855</v>
+        <v>0.1074787090317408</v>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.3403277687389276</v>
       </c>
       <c r="K57" t="n">
+        <v>10</v>
+      </c>
+      <c r="L57" t="n">
+        <v>11</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
         <v>4</v>
       </c>
-      <c r="L57" t="n">
-        <v>14</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0.6</v>
-      </c>
       <c r="O57" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="P57" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="R57" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.3</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="T57" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U57" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.22</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.1466666666666667</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.07333333333333333</v>
       </c>
     </row>
     <row r="58">
@@ -4522,55 +4508,61 @@
         <v>2012</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7933333333333334</v>
+        <v>0.76</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7715509928667823</v>
+        <v>0.7184294871794871</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1959438323974609</v>
+        <v>0.2383119761943817</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4696164429187775</v>
+        <v>0.01034864317625761</v>
       </c>
       <c r="I58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.02257346175611019</v>
+      </c>
+      <c r="K58" t="n">
+        <v>9</v>
+      </c>
+      <c r="L58" t="n">
+        <v>9</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
         <v>6</v>
       </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" t="n">
-        <v>14</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S58" t="n">
         <v>0.6</v>
       </c>
-      <c r="O58" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
       <c r="T58" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.6</v>
       </c>
       <c r="U58" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.25</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="59">
@@ -4593,55 +4585,61 @@
         <v>2012</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9133333333333333</v>
+        <v>0.86</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9025641025641025</v>
+        <v>0.8333573289455641</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1423480244754639</v>
+        <v>0.1537593530455645</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6407988137251898</v>
+        <v>0.4135391445390953</v>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>0.248744248664694</v>
       </c>
       <c r="K59" t="n">
+        <v>6</v>
+      </c>
+      <c r="L59" t="n">
         <v>3</v>
       </c>
-      <c r="L59" t="n">
-        <v>15</v>
-      </c>
       <c r="M59" t="n">
-        <v>0.8235294117647058</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>0.7</v>
+        <v>12</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="P59" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R59" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="S59" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="T59" t="n">
-        <v>0.24</v>
+        <v>0.72</v>
       </c>
       <c r="U59" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.3600000000000001</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.3800000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4664,54 +4662,60 @@
         <v>2012</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5966666666666667</v>
+        <v>0.59</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5267948717948717</v>
+        <v>0.5212393162393162</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3160468795061819</v>
+        <v>0.3115193386773867</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>10</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>15</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0.4</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
       <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>0.4</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>0.3</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>0.2</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4735,55 +4739,61 @@
         <v>2012</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8168440617353662</v>
+        <v>0.8347294372294373</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2222609874122116</v>
+        <v>0.2689844743435479</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01329423575621427</v>
+        <v>8.246480369543175e-06</v>
       </c>
       <c r="I61" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.01205566727739132</v>
+      </c>
+      <c r="K61" t="n">
         <v>9</v>
       </c>
-      <c r="J61" t="n">
-        <v>2</v>
-      </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
       <c r="L61" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="N61" t="n">
+        <v>9</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="P61" t="n">
         <v>0.9</v>
       </c>
-      <c r="O61" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="P61" t="n">
+      <c r="Q61" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R61" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.88</v>
-      </c>
       <c r="S61" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="T61" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.72</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.19</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -4819,7 +4829,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.514</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="3">
@@ -4829,7 +4839,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.696</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -4849,7 +4859,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.615</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="6">
@@ -4859,7 +4869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.625</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="7">
@@ -4869,7 +4879,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.644</v>
+        <v>0.648</v>
       </c>
     </row>
   </sheetData>
@@ -4945,25 +4955,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.538</v>
       </c>
       <c r="D2" t="n">
-        <v>0.658</v>
+        <v>0.624</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.499</v>
+        <v>0.46</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.987</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -4978,25 +4988,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.741</v>
+        <v>0.655</v>
       </c>
       <c r="E3" t="n">
-        <v>0.92</v>
+        <v>0.894</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639</v>
+        <v>0.539</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08</v>
+        <v>0.106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.613</v>
+        <v>0.717</v>
       </c>
       <c r="I3" t="n">
-        <v>0.187</v>
+        <v>0.228</v>
       </c>
     </row>
     <row r="4">
@@ -5014,22 +5024,22 @@
         <v>0.621</v>
       </c>
       <c r="D4" t="n">
-        <v>0.718</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>0.725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.616</v>
+        <v>0.653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.618</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -5044,25 +5054,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.57</v>
       </c>
       <c r="D5" t="n">
-        <v>0.729</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.908</v>
+        <v>0.7</v>
       </c>
       <c r="F5" t="n">
-        <v>0.622</v>
+        <v>0.517</v>
       </c>
       <c r="G5" t="n">
-        <v>0.092</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.613</v>
+        <v>0.583</v>
       </c>
       <c r="I5" t="n">
-        <v>0.197</v>
+        <v>0.357</v>
       </c>
     </row>
     <row r="6">
@@ -5077,25 +5087,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.61</v>
       </c>
       <c r="D6" t="n">
-        <v>0.738</v>
+        <v>0.671</v>
       </c>
       <c r="E6" t="n">
-        <v>0.86</v>
+        <v>0.825</v>
       </c>
       <c r="F6" t="n">
-        <v>0.708</v>
+        <v>0.607</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>0.175</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>0.225</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="7">
@@ -5110,25 +5120,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.648</v>
       </c>
       <c r="D7" t="n">
-        <v>0.752</v>
+        <v>0.647</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.67</v>
+        <v>0.505</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06</v>
+        <v>0.066</v>
       </c>
       <c r="H7" t="n">
-        <v>0.644</v>
+        <v>0.806</v>
       </c>
       <c r="I7" t="n">
-        <v>0.177</v>
+        <v>0.214</v>
       </c>
     </row>
   </sheetData>
@@ -5174,7 +5184,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="3">
@@ -5184,7 +5194,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -5204,7 +5214,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="6">
@@ -5214,7 +5224,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="7">
@@ -5224,7 +5234,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.648</v>
       </c>
     </row>
     <row r="8">
@@ -5239,7 +5249,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.537</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5259,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.706</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="10">
@@ -5259,7 +5269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.51</v>
+        <v>0.512</v>
       </c>
     </row>
     <row r="11">
@@ -5269,7 +5279,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.636</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="12">
@@ -5279,7 +5289,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.584</v>
+        <v>0.572</v>
       </c>
     </row>
     <row r="13">
@@ -5289,7 +5299,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.597</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12a/results_12a_final.xlsx
+++ b/outputs/results/12a/results_12a_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="all_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -554,48 +564,24 @@
       <c r="G2" t="n">
         <v>0.6382792115128209</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
         <v>2.227087997341149e-06</v>
       </c>
-      <c r="I2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -625,48 +611,24 @@
       <c r="G3" t="n">
         <v>0.639204</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,48 +658,24 @@
       <c r="G4" t="n">
         <v>0.6343255043029785</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>0.0007247853209264576</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,56 +697,32 @@
         <v>2008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5972222222222223</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6599885366826156</v>
+        <v>0.6709222742127154</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6080413644562611</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.009696280344509325</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
+        <v>0.6022725009764526</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8108108108108109</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1229166666666667</v>
-      </c>
+        <v>0.01345944385518387</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,48 +752,24 @@
       <c r="G6" t="n">
         <v>0.64</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -909,48 +799,24 @@
       <c r="G7" t="n">
         <v>0.6399903431451417</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>1.441656627305284e-06</v>
       </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -978,49 +844,55 @@
         <v>0.7895733600717869</v>
       </c>
       <c r="G8" t="n">
-        <v>0.223293979127919</v>
+        <v>0.2232589768259335</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2014106733770808</v>
+        <v>2.227087997341149e-06</v>
       </c>
       <c r="I8" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2010244167158451</v>
+      </c>
+      <c r="K8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +915,61 @@
         <v>2009</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.625</v>
       </c>
       <c r="F9" t="n">
-        <v>0.730835362280964</v>
+        <v>0.7634971610515089</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3761944036855912</v>
+        <v>0.4703116184770035</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04570979684019617</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.01612903225806452</v>
+      </c>
+      <c r="K9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +992,61 @@
         <v>2009</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7319402405360937</v>
+        <v>0.7375525355062893</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3580358922481537</v>
+        <v>0.3516033291816711</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00820888951420784</v>
+        <v>0.0007247853209264576</v>
       </c>
       <c r="I10" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.06595040857791901</v>
+      </c>
+      <c r="K10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1069,61 @@
         <v>2009</v>
       </c>
       <c r="E11" t="n">
-        <v>0.486111111111111</v>
+        <v>0.7430555555555556</v>
       </c>
       <c r="F11" t="n">
-        <v>0.609264137130985</v>
+        <v>0.8075918107627666</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2741606954812124</v>
+        <v>0.440130478595326</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3886823637074523</v>
+        <v>0.01345944385518387</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>0.002849947433218398</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7804878048780488</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>0.64</v>
+        <v>0.7586206896551724</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="R11" t="n">
-        <v>0.64</v>
+        <v>0.3125</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.2854166666666667</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2944444444444445</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.3034722222222222</v>
       </c>
     </row>
     <row r="12">
@@ -1256,54 +1146,60 @@
         <v>2009</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3125</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6925</v>
+        <v>0.6433522727272727</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5736267796116965</v>
+        <v>0.597905722679953</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>16</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.64</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
         <v>0.64</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1327,55 +1223,61 @@
         <v>2009</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6527777777777779</v>
+        <v>0.5694444444444444</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7912109815802271</v>
+        <v>0.6613085531048497</v>
       </c>
       <c r="G13" t="n">
-        <v>0.473175400123597</v>
+        <v>0.6006543359401034</v>
       </c>
       <c r="H13" t="n">
-        <v>6.283065748490748e-08</v>
+        <v>1.441656627305284e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>3.260398362557813e-08</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8205128205128205</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.8108108108108109</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="R13" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.72</v>
       </c>
-      <c r="S13" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.1555555555555556</v>
-      </c>
       <c r="U13" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.24375</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1229166666666667</v>
       </c>
     </row>
     <row r="14">
@@ -1404,49 +1306,55 @@
         <v>0.4843657067570111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4144737581190095</v>
+        <v>0.4144747482927156</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7833577863639724</v>
+        <v>0.2010244167158451</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>0.7833702235115346</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6428571428571429</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1377,61 @@
         <v>2010</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4266666666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>0.382668172470804</v>
+        <v>0.3889504613034025</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2545735890098271</v>
+        <v>0.2768933193140049</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3137136777324644</v>
+        <v>0.01612903225806452</v>
       </c>
       <c r="I15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.3698866352621407</v>
+      </c>
+      <c r="K15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -1540,55 +1454,61 @@
         <v>2010</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4466666666666667</v>
+        <v>0.5533333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.379942123094297</v>
+        <v>0.4864510541058529</v>
       </c>
       <c r="G16" t="n">
-        <v>0.306172251701355</v>
+        <v>0.3193759620189667</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1123559102416039</v>
+        <v>0.06595040857791901</v>
       </c>
       <c r="I16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.06324560940265656</v>
+      </c>
+      <c r="K16" t="n">
+        <v>9</v>
+      </c>
+      <c r="L16" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="n">
-        <v>14</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" t="n">
-        <v>0.5882352941176471</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="R16" t="n">
-        <v>0.44</v>
+        <v>0.1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.28</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2133333333333333</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.1566666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -1611,55 +1531,61 @@
         <v>2010</v>
       </c>
       <c r="E17" t="n">
-        <v>0.52</v>
+        <v>0.5133333333333333</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4808495670995671</v>
+        <v>0.4245671719584763</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4480604958059615</v>
+        <v>0.4742782682256643</v>
       </c>
       <c r="H17" t="n">
-        <v>1.584038067466776e-12</v>
+        <v>0.002849947433218398</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J17" t="n">
-        <v>12</v>
+        <v>5.350693781743878e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M17" t="n">
-        <v>0.625</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O17" t="n">
         <v>0.4545454545454545</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="R17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.52</v>
       </c>
-      <c r="S17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.16</v>
-      </c>
       <c r="U17" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.49</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4933333333333333</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.4966666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -1682,55 +1608,61 @@
         <v>2010</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5066666666666666</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.388621494554386</v>
+        <v>0.2938353297422371</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7879234167893957</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5310173697270471</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -1753,54 +1685,60 @@
         <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4866666666666666</v>
+        <v>0.4133333333333333</v>
       </c>
       <c r="F19" t="n">
-        <v>0.459244071146245</v>
+        <v>0.3642118992118992</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3514883211898782</v>
+        <v>0.428957336566944</v>
       </c>
       <c r="H19" t="n">
-        <v>7.724365950953985e-08</v>
+        <v>3.260398362557813e-08</v>
       </c>
       <c r="I19" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.390212894340872e-06</v>
+      </c>
+      <c r="K19" t="n">
         <v>10</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>14</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="N19" t="n">
-        <v>1</v>
-      </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.44</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.28</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>0.1866666666666667</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>0.09333333333333334</v>
       </c>
     </row>
@@ -1830,49 +1768,55 @@
         <v>0.5675036075036075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2170654818769425</v>
+        <v>0.2166253508234882</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4083412920571219</v>
+        <v>0.7833702235115346</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>0.4096637298652834</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="S20" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1895,55 +1839,61 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7466666666666666</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7107798481711525</v>
+        <v>0.7021230158730157</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2148953671258025</v>
+        <v>0.234208243670115</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3182923340208793</v>
+        <v>0.3698866352621407</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J21" t="n">
+        <v>0.2518165360693508</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>3</v>
-      </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7368421052631579</v>
+        <v>8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R21" t="n">
         <v>0.8</v>
       </c>
       <c r="S21" t="n">
-        <v>0.25</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.6533333333333334</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.7266666666666668</v>
       </c>
     </row>
     <row r="22">
@@ -1966,55 +1916,61 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6822619047619047</v>
+        <v>0.6755447330447331</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2379890829324722</v>
+        <v>0.2026104331016541</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09450928121805191</v>
+        <v>0.06324560940265656</v>
       </c>
       <c r="I22" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4474846422672272</v>
+      </c>
+      <c r="K22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U22" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6126984126984126</v>
+        <v>0.6005939229852273</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2549496525175192</v>
+        <v>0.2046067346920317</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1290546634897831</v>
+        <v>5.350693781743878e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>0.2432305308474809</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -2108,55 +2070,61 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.54</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4533333333333334</v>
+        <v>0.3866666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3877373884297521</v>
+        <v>0.48</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.5310173697270471</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5714285714285714</v>
+        <v>8</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1</v>
+        <v>0.6399999999999999</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.6933333333333335</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.7466666666666667</v>
       </c>
     </row>
     <row r="25">
@@ -2179,55 +2147,61 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7083241758241758</v>
+        <v>0.7001037851037851</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2719960540167289</v>
+        <v>0.1981996404528197</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03962087894369956</v>
+        <v>1.390212894340872e-06</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>0.3083718542194023</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6956521739130435</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.2266666666666667</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.2133333333333333</v>
+      <c r="W25" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -2256,49 +2230,55 @@
         <v>0.7565384615384615</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1956060252987059</v>
+        <v>0.195122044201516</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5851407395184636</v>
+        <v>0.4096637298652834</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0.5795566651666948</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.2</v>
       </c>
-      <c r="R26" t="n">
-        <v>0.76</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.68</v>
       </c>
       <c r="U26" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8733333333333334</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8391575091575091</v>
+        <v>0.8733974358974358</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1639718747066577</v>
+        <v>0.1611253871080324</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5415036188475644</v>
+        <v>0.2518165360693508</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.3174474385207861</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="R27" t="n">
-        <v>0.84</v>
+        <v>0.1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.28</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="U27" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.1366666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2012</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.84</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8732874968169085</v>
+        <v>0.8168109668109668</v>
       </c>
       <c r="G28" t="n">
-        <v>0.155405193567276</v>
+        <v>0.1866668909788132</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6614319682121277</v>
+        <v>0.4474846422672272</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1356123834848404</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L28" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8235294117647058</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7</v>
+        <v>11</v>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R28" t="n">
-        <v>0.88</v>
+        <v>0.2</v>
       </c>
       <c r="S28" t="n">
-        <v>0.21</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T28" t="n">
-        <v>0.24</v>
+        <v>0.76</v>
       </c>
       <c r="U28" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.2133333333333334</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.2066666666666667</v>
       </c>
     </row>
     <row r="29">
@@ -2463,55 +2455,61 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.84</v>
+        <v>0.8000000000000002</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8352453102453102</v>
+        <v>0.7693162393162393</v>
       </c>
       <c r="G29" t="n">
-        <v>0.166953586544577</v>
+        <v>0.1874324625239185</v>
       </c>
       <c r="H29" t="n">
-        <v>0.654490273882216</v>
+        <v>0.2432305308474809</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J29" t="n">
+        <v>0.052438125911382</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="n">
         <v>3</v>
       </c>
-      <c r="K29" t="n">
-        <v>2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>12</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.7619047619047619</v>
-      </c>
       <c r="N29" t="n">
+        <v>13</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.7368421052631579</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="T29" t="n">
         <v>0.8</v>
       </c>
-      <c r="O29" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.2</v>
-      </c>
       <c r="U29" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.2833333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6383333333333334</v>
+        <v>0.6689393939393939</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2226751315721354</v>
+        <v>0.209706699861893</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1696014828544953</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5062240663900414</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.86</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8955542986425339</v>
+        <v>0.8367748917748917</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1465093221462065</v>
+        <v>0.1814996244024002</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1188784941635189</v>
+        <v>0.3083718542194023</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>2011</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0.1277111389718512</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>14</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="T31" t="n">
         <v>0.8</v>
       </c>
-      <c r="N31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.1866666666666667</v>
-      </c>
       <c r="U31" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -2684,48 +2694,24 @@
       <c r="G32" t="n">
         <v>0.6397517261347714</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>1.163216072620251e-07</v>
       </c>
-      <c r="I32" t="n">
-        <v>16</v>
-      </c>
-      <c r="J32" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2747,56 +2733,32 @@
         <v>2008</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.4513888888888889</v>
       </c>
       <c r="F33" t="n">
-        <v>0.64</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16</v>
-      </c>
+        <v>0.63764</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>9</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2826,48 +2788,24 @@
       <c r="G34" t="n">
         <v>0.633694589138031</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
         <v>0.004945225547999144</v>
       </c>
-      <c r="I34" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2889,56 +2827,32 @@
         <v>2008</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4375</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6099316826272843</v>
+        <v>0.7167970607608765</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5970282271938142</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.01037416278161608</v>
-      </c>
-      <c r="I35" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5947470179573791</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.0123665026744801</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2968,48 +2882,24 @@
       <c r="G36" t="n">
         <v>0.64</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>16</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3039,48 +2929,24 @@
       <c r="G37" t="n">
         <v>0.6399850529731999</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>16</v>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3111,46 +2977,52 @@
         <v>0.6399149582541784</v>
       </c>
       <c r="H38" t="n">
+        <v>1.163216072620251e-07</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J38" t="n">
         <v>5.774910310799749e-07</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>16</v>
       </c>
-      <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R38" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
@@ -3173,54 +3045,60 @@
         <v>2009</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4409722222222222</v>
+        <v>0.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6120833333333334</v>
+        <v>0.64</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6361520000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>16</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>9</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0.64</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>0.64</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.3</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.2</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3253,46 +3131,52 @@
         <v>0.6338368058204651</v>
       </c>
       <c r="H40" t="n">
+        <v>0.004945225547999144</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.004833243321627378</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>16</v>
       </c>
-      <c r="J40" t="n">
+      <c r="N40" t="n">
         <v>9</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
       <c r="O40" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3199,61 @@
         <v>2009</v>
       </c>
       <c r="E41" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6103123469667587</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.626583654870239</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.0123665026744801</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.001233229579275246</v>
+      </c>
+      <c r="K41" t="n">
+        <v>6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>10</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="P41" t="n">
         <v>0.375</v>
       </c>
-      <c r="F41" t="n">
-        <v>0.5702398439866471</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.6164883184918493</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.001678897141775105</v>
-      </c>
-      <c r="I41" t="n">
-        <v>16</v>
-      </c>
-      <c r="J41" t="n">
-        <v>9</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N41" t="n">
-        <v>1</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="R41" t="n">
-        <v>0.64</v>
+        <v>0.625</v>
       </c>
       <c r="S41" t="n">
-        <v>0.3</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1</v>
+        <v>0.6041666666666666</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.6180555555555556</v>
       </c>
     </row>
     <row r="42">
@@ -3398,42 +3288,48 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>16</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>9</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.64</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>0.64</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.3</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.2</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3466,46 +3362,52 @@
         <v>0.6398924456781397</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J43" t="n">
         <v>1.447725522269862e-11</v>
       </c>
-      <c r="I43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0.75</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2104166666666666</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1611111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1118055555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
@@ -3537,46 +3439,52 @@
         <v>0.3997083474543894</v>
       </c>
       <c r="H44" t="n">
+        <v>5.774910310799749e-07</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J44" t="n">
         <v>9.269796436416404e-06</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>10</v>
       </c>
-      <c r="J44" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
@@ -3599,54 +3507,60 @@
         <v>2010</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="F45" t="n">
         <v>0.4</v>
       </c>
       <c r="G45" t="n">
+        <v>0.400004</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" t="n">
+        <v>15</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.4</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" t="n">
-        <v>15</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.4</v>
       </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.2</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3679,46 +3593,52 @@
         <v>0.3964213132858276</v>
       </c>
       <c r="H46" t="n">
+        <v>0.004833243321627378</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.004498659633100033</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="n">
+      <c r="N46" t="n">
         <v>15</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
       <c r="O46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U46" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
@@ -3741,55 +3661,61 @@
         <v>2010</v>
       </c>
       <c r="E47" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5126449275362319</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.396113616147994</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.001233229579275246</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.001204922186280358</v>
+      </c>
+      <c r="K47" t="n">
+        <v>7</v>
+      </c>
+      <c r="L47" t="n">
+        <v>7</v>
+      </c>
+      <c r="M47" t="n">
+        <v>3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>8</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F47" t="n">
-        <v>0.4867383107088989</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.3992378639494475</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.0003971452859503358</v>
-      </c>
-      <c r="I47" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>6</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3</v>
-      </c>
-      <c r="L47" t="n">
-        <v>9</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.6086956521739131</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.32</v>
-      </c>
       <c r="U47" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.35</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.3166666666666667</v>
       </c>
     </row>
     <row r="48">
@@ -3824,42 +3750,48 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>15</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0.4</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>0.4</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.3</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>0.2</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3892,46 +3824,52 @@
         <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.447725522269862e-11</v>
       </c>
       <c r="I49" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
         <v>10</v>
       </c>
-      <c r="J49" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.5714285714285714</v>
-      </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.3</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T49" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9066666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -3960,49 +3898,55 @@
         <v>0.7188704177323103</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2171061075379025</v>
+        <v>0.2170991847472247</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4888998500171703</v>
+        <v>9.269796436416404e-06</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>2010</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0.4888003189252604</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +3969,61 @@
         <v>2011</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.7133333333333334</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6406762192056309</v>
+        <v>0.6535183770477888</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2633358424813289</v>
+        <v>0.2461008339955718</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06085160778335204</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>0.06903522871664038</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4046,61 @@
         <v>2011</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.7466666666666666</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7201984126984127</v>
+        <v>0.7099716000373893</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2852432727813721</v>
+        <v>0.2822245359420776</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01487493608146906</v>
+        <v>0.004498659633100033</v>
       </c>
       <c r="I52" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.009246326051652431</v>
+      </c>
+      <c r="K52" t="n">
         <v>9</v>
       </c>
-      <c r="J52" t="n">
-        <v>6</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M52" t="n">
-        <v>0.72</v>
+        <v>1</v>
       </c>
       <c r="N52" t="n">
+        <v>7</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P52" t="n">
         <v>0.9</v>
       </c>
-      <c r="O52" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="P52" t="n">
+      <c r="Q52" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="R52" t="n">
         <v>0.1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.72</v>
-      </c>
       <c r="S52" t="n">
-        <v>0.19</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T52" t="n">
-        <v>0.16</v>
+        <v>0.64</v>
       </c>
       <c r="U52" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4123,61 @@
         <v>2011</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.7266666666666667</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8210081585081584</v>
+        <v>0.6489700577200577</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2202869608750037</v>
+        <v>0.2366746431371681</v>
       </c>
       <c r="H53" t="n">
-        <v>1.713269544996963e-05</v>
+        <v>0.001204922186280358</v>
       </c>
       <c r="I53" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5008851747182371</v>
+      </c>
+      <c r="K53" t="n">
         <v>10</v>
       </c>
-      <c r="J53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U53" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="54">
@@ -4238,54 +4200,60 @@
         <v>2011</v>
       </c>
       <c r="E54" t="n">
-        <v>0.5866666666666667</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="F54" t="n">
-        <v>0.4733333333333333</v>
+        <v>0.4533333333333334</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3350785506919857</v>
+        <v>0.3548833409373043</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>10</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>15</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0.4</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
         <v>0.4</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>0.2</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4309,55 +4277,61 @@
         <v>2011</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8733333333333334</v>
       </c>
       <c r="F55" t="n">
-        <v>0.780877684407096</v>
+        <v>0.8337301587301587</v>
       </c>
       <c r="G55" t="n">
-        <v>0.282606541385438</v>
+        <v>0.2846608626500789</v>
       </c>
       <c r="H55" t="n">
-        <v>5.530121171447283e-07</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J55" t="n">
+        <v>2.726503332705406e-07</v>
+      </c>
+      <c r="K55" t="n">
         <v>10</v>
       </c>
-      <c r="J55" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U55" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
@@ -4380,55 +4354,61 @@
         <v>2012</v>
       </c>
       <c r="E56" t="n">
-        <v>0.82</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8052686202686202</v>
+        <v>0.7991558441558442</v>
       </c>
       <c r="G56" t="n">
-        <v>0.24675586501407</v>
+        <v>0.2136318915819789</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4980951475015878</v>
+        <v>0.4888003189252604</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J56" t="n">
+        <v>0.4682028592212699</v>
+      </c>
+      <c r="K56" t="n">
+        <v>6</v>
+      </c>
+      <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
+        <v>4</v>
+      </c>
+      <c r="N56" t="n">
         <v>13</v>
       </c>
-      <c r="M56" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O56" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P56" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q56" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S56" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="R56" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.25</v>
-      </c>
       <c r="T56" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="U56" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.32</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="57">
@@ -4451,55 +4431,61 @@
         <v>2012</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7988220551378445</v>
+        <v>0.8017632316084328</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1772604300135964</v>
+        <v>0.1811973393212679</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4668391189611855</v>
+        <v>0.06903522871664038</v>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.4196821291350996</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7058823529411765</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
+        <v>5</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="T57" t="n">
         <v>0.6</v>
       </c>
-      <c r="O57" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q57" t="n">
+      <c r="U57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="W57" t="n">
         <v>0.06666666666666667</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T57" t="n">
-        <v>0.3333333333333334</v>
-      </c>
-      <c r="U57" t="n">
-        <v>0.3666666666666667</v>
       </c>
     </row>
     <row r="58">
@@ -4522,55 +4508,61 @@
         <v>2012</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7933333333333334</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7715509928667823</v>
+        <v>0.8044064707222601</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1959438323974609</v>
+        <v>0.2104670107364655</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4696164429187775</v>
+        <v>0.009246326051652431</v>
       </c>
       <c r="I58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.1243003532290459</v>
+      </c>
+      <c r="K58" t="n">
+        <v>9</v>
+      </c>
+      <c r="L58" t="n">
+        <v>9</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1</v>
+      </c>
+      <c r="N58" t="n">
         <v>6</v>
       </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4</v>
-      </c>
-      <c r="L58" t="n">
-        <v>14</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S58" t="n">
         <v>0.6</v>
       </c>
-      <c r="O58" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3</v>
-      </c>
       <c r="T58" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.6</v>
       </c>
       <c r="U58" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.25</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="59">
@@ -4593,55 +4585,61 @@
         <v>2012</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9133333333333333</v>
+        <v>0.8066666666666666</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9025641025641025</v>
+        <v>0.7507282913165266</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1423480244754639</v>
+        <v>0.1848890005808913</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6407988137251898</v>
+        <v>0.5008851747182371</v>
       </c>
       <c r="I59" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.3436698929970818</v>
+      </c>
+      <c r="K59" t="n">
         <v>7</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
+        <v>5</v>
+      </c>
+      <c r="M59" t="n">
         <v>3</v>
       </c>
-      <c r="L59" t="n">
-        <v>15</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.8235294117647058</v>
-      </c>
       <c r="N59" t="n">
+        <v>10</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="P59" t="n">
         <v>0.7</v>
       </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="R59" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.88</v>
-      </c>
       <c r="S59" t="n">
-        <v>0.21</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T59" t="n">
-        <v>0.24</v>
+        <v>0.68</v>
       </c>
       <c r="U59" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.3066666666666666</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.3033333333333333</v>
       </c>
     </row>
     <row r="60">
@@ -4664,10 +4662,10 @@
         <v>2012</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5966666666666667</v>
+        <v>0.6233333333333333</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5267948717948717</v>
+        <v>0.535</v>
       </c>
       <c r="G60" t="n">
         <v>0.3160468795061819</v>
@@ -4676,42 +4674,48 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>10</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>15</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0.4</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
       <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>0.4</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>0.3</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>0.2</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4735,55 +4739,61 @@
         <v>2012</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8168440617353662</v>
+        <v>0.7711643911643911</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2222609874122116</v>
+        <v>0.1977765242691885</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01329423575621427</v>
+        <v>2.726503332705406e-07</v>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>0.05041835364195921</v>
       </c>
       <c r="K61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L61" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8571428571428571</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P61" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W61" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0.1066666666666667</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0.1033333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -4819,7 +4829,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.514</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="3">
@@ -4829,7 +4839,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.696</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="4">
@@ -4849,7 +4859,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.615</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="6">
@@ -4859,7 +4869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.625</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="7">
@@ -4869,7 +4879,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.644</v>
+        <v>0.638</v>
       </c>
     </row>
   </sheetData>
@@ -4945,25 +4955,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.503</v>
       </c>
       <c r="D2" t="n">
-        <v>0.658</v>
+        <v>0.543</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.499</v>
+        <v>0.443</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>0.987</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="3">
@@ -4978,25 +4988,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.672</v>
       </c>
       <c r="D3" t="n">
-        <v>0.741</v>
+        <v>0.669</v>
       </c>
       <c r="E3" t="n">
-        <v>0.92</v>
+        <v>0.884</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639</v>
+        <v>0.597</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="H3" t="n">
-        <v>0.613</v>
+        <v>0.667</v>
       </c>
       <c r="I3" t="n">
-        <v>0.187</v>
+        <v>0.226</v>
       </c>
     </row>
     <row r="4">
@@ -5014,22 +5024,22 @@
         <v>0.621</v>
       </c>
       <c r="D4" t="n">
-        <v>0.718</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>0.725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.616</v>
+        <v>0.653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.618</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -5044,25 +5054,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.671</v>
       </c>
       <c r="D5" t="n">
-        <v>0.729</v>
+        <v>0.63</v>
       </c>
       <c r="E5" t="n">
-        <v>0.908</v>
+        <v>0.722</v>
       </c>
       <c r="F5" t="n">
-        <v>0.622</v>
+        <v>0.61</v>
       </c>
       <c r="G5" t="n">
-        <v>0.092</v>
+        <v>0.278</v>
       </c>
       <c r="H5" t="n">
-        <v>0.613</v>
+        <v>0.456</v>
       </c>
       <c r="I5" t="n">
-        <v>0.197</v>
+        <v>0.314</v>
       </c>
     </row>
     <row r="6">
@@ -5077,25 +5087,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.641</v>
       </c>
       <c r="D6" t="n">
-        <v>0.738</v>
+        <v>0.588</v>
       </c>
       <c r="E6" t="n">
-        <v>0.86</v>
+        <v>0.775</v>
       </c>
       <c r="F6" t="n">
-        <v>0.708</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>0.225</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="I6" t="n">
-        <v>0.225</v>
+        <v>0.307</v>
       </c>
     </row>
     <row r="7">
@@ -5110,25 +5120,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.638</v>
       </c>
       <c r="D7" t="n">
-        <v>0.752</v>
+        <v>0.675</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="F7" t="n">
-        <v>0.67</v>
+        <v>0.545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06</v>
+        <v>0.075</v>
       </c>
       <c r="H7" t="n">
-        <v>0.644</v>
+        <v>0.733</v>
       </c>
       <c r="I7" t="n">
-        <v>0.177</v>
+        <v>0.207</v>
       </c>
     </row>
   </sheetData>
@@ -5174,7 +5184,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="3">
@@ -5184,7 +5194,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="4">
@@ -5204,7 +5214,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="6">
@@ -5214,7 +5224,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.641</v>
       </c>
     </row>
     <row r="7">
@@ -5224,7 +5234,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.638</v>
       </c>
     </row>
     <row r="8">
@@ -5239,7 +5249,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.537</v>
+        <v>0.538</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5259,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.706</v>
+        <v>0.716</v>
       </c>
     </row>
     <row r="10">
@@ -5259,7 +5269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.51</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="11">
@@ -5269,7 +5279,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.636</v>
+        <v>0.642</v>
       </c>
     </row>
     <row r="12">
@@ -5279,7 +5289,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.584</v>
+        <v>0.589</v>
       </c>
     </row>
     <row r="13">
@@ -5289,7 +5299,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.617</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/results/12a/results_12a_final.xlsx
+++ b/outputs/results/12a/results_12a_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="all_results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="all_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="auroc_pivot_baseline" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mean_metrics_baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="macro_standalone_vs_rt1" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U61"/>
+  <dimension ref="A1:W61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,65 +462,75 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>threshold_from_year</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>test_optimal_threshold</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>miss_rate</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>false_alarm_rate</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>loss_07</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>loss_08</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>loss_09</t>
         </is>
@@ -554,48 +564,24 @@
       <c r="G2" t="n">
         <v>0.6382792115128209</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
         <v>2.227087997341149e-06</v>
       </c>
-      <c r="I2" t="n">
-        <v>16</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -625,48 +611,24 @@
       <c r="G3" t="n">
         <v>0.639204</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16</v>
-      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -696,48 +658,24 @@
       <c r="G4" t="n">
         <v>0.6343255043029785</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
         <v>0.0007247853209264576</v>
       </c>
-      <c r="I4" t="n">
-        <v>16</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -759,56 +697,32 @@
         <v>2008</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.451388888888889</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6599885366826156</v>
+        <v>0.6263160025202359</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6080413644562611</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.009696280344509325</v>
-      </c>
-      <c r="I5" t="n">
-        <v>15</v>
-      </c>
+        <v>0.6118917106993242</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.8108108108108109</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.24375</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1229166666666667</v>
-      </c>
+        <v>0.004494072158938133</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -838,48 +752,24 @@
       <c r="G6" t="n">
         <v>0.64</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -909,48 +799,24 @@
       <c r="G7" t="n">
         <v>0.6399903431451417</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>1.441656627305284e-06</v>
       </c>
-      <c r="I7" t="n">
-        <v>16</v>
-      </c>
-      <c r="J7" t="n">
-        <v>8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.1777777777777778</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.08888888888888889</v>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -978,49 +844,55 @@
         <v>0.7895733600717869</v>
       </c>
       <c r="G8" t="n">
-        <v>0.223293979127919</v>
+        <v>0.2232605000943329</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2014106733770808</v>
+        <v>2.227087997341149e-06</v>
       </c>
       <c r="I8" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2010154484919004</v>
+      </c>
+      <c r="K8" t="n">
         <v>16</v>
       </c>
-      <c r="J8" t="n">
-        <v>8</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R8" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U8" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1043,55 +915,61 @@
         <v>2009</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5416666666666667</v>
+        <v>0.6805555555555556</v>
       </c>
       <c r="F9" t="n">
-        <v>0.730835362280964</v>
+        <v>0.8246852106227106</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3761944036855912</v>
+        <v>0.2743826448018671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04570979684019617</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2057858513621593</v>
+      </c>
+      <c r="K9" t="n">
         <v>16</v>
       </c>
-      <c r="J9" t="n">
-        <v>8</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R9" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U9" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1114,55 +992,61 @@
         <v>2009</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6319444444444444</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7319402405360937</v>
+        <v>0.8309415634983091</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3580358922481537</v>
+        <v>0.2920210957527161</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00820888951420784</v>
+        <v>0.0007247853209264576</v>
       </c>
       <c r="I10" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.1200620159506798</v>
+      </c>
+      <c r="K10" t="n">
         <v>16</v>
       </c>
-      <c r="J10" t="n">
-        <v>8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R10" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U10" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1185,55 +1069,61 @@
         <v>2009</v>
       </c>
       <c r="E11" t="n">
-        <v>0.486111111111111</v>
+        <v>0.7152777777777779</v>
       </c>
       <c r="F11" t="n">
-        <v>0.609264137130985</v>
+        <v>0.7805778336468874</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2741606954812124</v>
+        <v>0.5637213955370517</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3886823637074523</v>
+        <v>0.004494072158938133</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J11" t="n">
-        <v>9</v>
+        <v>2.046652925709817e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7804878048780488</v>
+        <v>10</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
-        <v>0.64</v>
+        <v>0.5</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R11" t="n">
-        <v>0.64</v>
+        <v>0.625</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2</v>
+        <v>0.52</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.5041666666666667</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.5847222222222223</v>
       </c>
     </row>
     <row r="12">
@@ -1256,54 +1146,60 @@
         <v>2009</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3125</v>
+        <v>0.5034722222222222</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6925</v>
+        <v>0.7075</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5736267796116965</v>
+        <v>0.5504038293329784</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
         <v>16</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>9</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.64</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
         <v>0.64</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.3</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.2</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1327,55 +1223,61 @@
         <v>2009</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6527777777777779</v>
+        <v>0.6736111111111112</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7912109815802271</v>
+        <v>0.7561828153020609</v>
       </c>
       <c r="G13" t="n">
-        <v>0.473175400123597</v>
+        <v>0.5127477992137195</v>
       </c>
       <c r="H13" t="n">
-        <v>6.283065748490748e-08</v>
+        <v>1.441656627305284e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>1.830731252603754e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8205128205128205</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6956521739130435</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.9375</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>0.72</v>
+        <v>0.0625</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1555555555555556</v>
+        <v>0.76</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07777777777777778</v>
+        <v>0.2104166666666666</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.1611111111111111</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.1118055555555556</v>
       </c>
     </row>
     <row r="14">
@@ -1404,49 +1306,55 @@
         <v>0.4843657067570111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4144737581190095</v>
+        <v>0.4144754284614636</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7833577863639724</v>
+        <v>0.2010154484919004</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>2009</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>0.7833787109695622</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6428571428571429</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="15">
@@ -1469,55 +1377,61 @@
         <v>2010</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.4533333333333334</v>
       </c>
       <c r="F15" t="n">
-        <v>0.382668172470804</v>
+        <v>0.3764377779083662</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2545735890098271</v>
+        <v>0.2530799219479195</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3137136777324644</v>
+        <v>0.2057858513621593</v>
       </c>
       <c r="I15" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.4588494542660833</v>
+      </c>
+      <c r="K15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>12</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M15" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="16">
@@ -1540,54 +1454,60 @@
         <v>2010</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4466666666666667</v>
+        <v>0.5133333333333333</v>
       </c>
       <c r="F16" t="n">
-        <v>0.379942123094297</v>
+        <v>0.4304616298733946</v>
       </c>
       <c r="G16" t="n">
-        <v>0.306172251701355</v>
+        <v>0.2762515246868134</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1123559102416039</v>
+        <v>0.1200620159506798</v>
       </c>
       <c r="I16" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1422493308782578</v>
+      </c>
+      <c r="K16" t="n">
         <v>10</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>14</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
         <v>0.5882352941176471</v>
       </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>0.44</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.28</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.1866666666666667</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.09333333333333334</v>
       </c>
     </row>
@@ -1614,52 +1534,58 @@
         <v>0.52</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4808495670995671</v>
+        <v>0.4829628122658813</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4480604958059615</v>
+        <v>0.3808575514342488</v>
       </c>
       <c r="H17" t="n">
-        <v>1.584038067466776e-12</v>
+        <v>2.046652925709817e-06</v>
       </c>
       <c r="I17" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.258060123803269e-25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>5</v>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" t="n">
         <v>10</v>
       </c>
-      <c r="J17" t="n">
-        <v>12</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
       <c r="O17" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8</v>
+        <v>0.375</v>
       </c>
       <c r="R17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.52</v>
       </c>
-      <c r="S17" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.16</v>
-      </c>
       <c r="U17" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.59</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.6266666666666666</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.6633333333333333</v>
       </c>
     </row>
     <row r="18">
@@ -1682,55 +1608,61 @@
         <v>2010</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>0.388621494554386</v>
+        <v>0.2608942395920757</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7879234167893957</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.4713656387665198</v>
+      </c>
+      <c r="K18" t="n">
         <v>10</v>
       </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5882352941176471</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R18" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -1753,55 +1685,61 @@
         <v>2010</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4866666666666666</v>
+        <v>0.48</v>
       </c>
       <c r="F19" t="n">
-        <v>0.459244071146245</v>
+        <v>0.4012387504435559</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3514883211898782</v>
+        <v>0.4270426502840124</v>
       </c>
       <c r="H19" t="n">
-        <v>7.724365950953985e-08</v>
+        <v>1.830731252603754e-06</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>2009</v>
       </c>
       <c r="J19" t="n">
+        <v>1.138507935827826e-08</v>
+      </c>
+      <c r="K19" t="n">
+        <v>9</v>
+      </c>
+      <c r="L19" t="n">
         <v>14</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
       <c r="M19" t="n">
-        <v>0.5882352941176471</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
         <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="Q19" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0.28</v>
-      </c>
       <c r="T19" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09333333333333334</v>
+        <v>0.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.1833333333333333</v>
       </c>
     </row>
     <row r="20">
@@ -1830,49 +1768,55 @@
         <v>0.5675036075036075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2170654818769425</v>
+        <v>0.2166591379577911</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4083412920571219</v>
+        <v>0.7833787109695622</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J20" t="n">
-        <v>6</v>
+        <v>0.4095659393807867</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>9</v>
       </c>
-      <c r="M20" t="n">
-        <v>0.6666666666666666</v>
-      </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="S20" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U20" t="n">
-        <v>0.22</v>
+        <v>0.63</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.7200000000000001</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1895,55 +1839,61 @@
         <v>2011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7533333333333333</v>
+        <v>0.7066666666666668</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7107798481711525</v>
+        <v>0.639514652014652</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2148953671258025</v>
+        <v>0.2133291112294517</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3182923340208793</v>
+        <v>0.4588494542660833</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>2010</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>0.2657002487578741</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7368421052631579</v>
+        <v>7</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7</v>
+        <v>14</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="P21" t="n">
         <v>0.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="S21" t="n">
-        <v>0.25</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.68</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.5099999999999999</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5733333333333333</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.6366666666666667</v>
       </c>
     </row>
     <row r="22">
@@ -1966,55 +1916,61 @@
         <v>2011</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.7933333333333333</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6822619047619047</v>
+        <v>0.6855050505050505</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2379890829324722</v>
+        <v>0.2445040941238403</v>
       </c>
       <c r="H22" t="n">
-        <v>0.09450928121805191</v>
+        <v>0.1422493308782578</v>
       </c>
       <c r="I22" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.2033257633447647</v>
+      </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" t="n">
         <v>10</v>
       </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>9</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.7692307692307693</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
       <c r="O22" t="n">
-        <v>0.625</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="R22" t="n">
-        <v>0.76</v>
+        <v>0.2</v>
       </c>
       <c r="S22" t="n">
-        <v>0.12</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="T22" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.72</v>
       </c>
       <c r="U22" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.24</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.2266666666666667</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.2133333333333333</v>
       </c>
     </row>
     <row r="23">
@@ -2037,55 +1993,61 @@
         <v>2011</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.7266666666666668</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6126984126984126</v>
+        <v>0.640016095016095</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2549496525175192</v>
+        <v>0.2069208495115456</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1290546634897831</v>
+        <v>1.258060123803269e-25</v>
       </c>
       <c r="I23" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J23" t="n">
-        <v>6</v>
+        <v>0.3440595527833483</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0.5714285714285714</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>0.24</v>
+        <v>0.4</v>
       </c>
       <c r="U23" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="24">
@@ -2108,55 +2070,61 @@
         <v>2011</v>
       </c>
       <c r="E24" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4533333333333334</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3877373884297521</v>
+        <v>0.3244048890098389</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.4713656387665198</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>2010</v>
       </c>
       <c r="J24" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5714285714285714</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="O24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P24" t="n">
         <v>0.4</v>
       </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2</v>
+        <v>0.68</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1</v>
+        <v>0.46</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.5066666666666666</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.5533333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -2179,55 +2147,61 @@
         <v>2011</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.8133333333333332</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7083241758241758</v>
+        <v>0.6880447330447331</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2719960540167289</v>
+        <v>0.1825409175249425</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03962087894369956</v>
+        <v>1.138507935827826e-08</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>2010</v>
       </c>
       <c r="J25" t="n">
-        <v>5</v>
+        <v>0.382114044373813</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6956521739130435</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V25" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.2266666666666667</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0.2133333333333333</v>
+      <c r="W25" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="26">
@@ -2256,49 +2230,55 @@
         <v>0.7565384615384615</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1956060252987059</v>
+        <v>0.1951196012995978</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5851407395184636</v>
+        <v>0.4095659393807867</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0.5795227140932604</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.7</v>
+        <v>9</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="Q26" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.2</v>
       </c>
-      <c r="R26" t="n">
-        <v>0.76</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="T26" t="n">
-        <v>0.28</v>
+        <v>0.68</v>
       </c>
       <c r="U26" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
@@ -2321,55 +2301,61 @@
         <v>2012</v>
       </c>
       <c r="E27" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8766666666666667</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8391575091575091</v>
+        <v>0.8532142857142856</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1639718747066577</v>
+        <v>0.1774639346667319</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5415036188475644</v>
+        <v>0.2657002487578741</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.3146853146853147</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.6</v>
+        <v>8</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="R27" t="n">
-        <v>0.84</v>
+        <v>0.1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.28</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3200000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="U27" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.1733333333333333</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.1366666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -2392,55 +2378,61 @@
         <v>2012</v>
       </c>
       <c r="E28" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8533333333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8732874968169085</v>
+        <v>0.8511217948717948</v>
       </c>
       <c r="G28" t="n">
-        <v>0.155405193567276</v>
+        <v>0.1629297435283661</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6614319682121277</v>
+        <v>0.2033257633447647</v>
       </c>
       <c r="I28" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.8006041049957275</v>
+      </c>
+      <c r="K28" t="n">
+        <v>9</v>
+      </c>
+      <c r="L28" t="n">
+        <v>8</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1</v>
+      </c>
+      <c r="N28" t="n">
         <v>7</v>
       </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" t="n">
-        <v>15</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="R28" t="n">
-        <v>0.88</v>
+        <v>0.1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.21</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="T28" t="n">
-        <v>0.24</v>
+        <v>0.64</v>
       </c>
       <c r="U28" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -2463,56 +2455,62 @@
         <v>2012</v>
       </c>
       <c r="E29" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8352453102453102</v>
+        <v>0.8063827349121467</v>
       </c>
       <c r="G29" t="n">
-        <v>0.166953586544577</v>
+        <v>0.184750559319982</v>
       </c>
       <c r="H29" t="n">
-        <v>0.654490273882216</v>
+        <v>0.3440595527833483</v>
       </c>
       <c r="I29" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.3721029289261683</v>
+      </c>
+      <c r="K29" t="n">
         <v>8</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>3</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>12</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.8</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.7272727272727273</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.8</v>
       </c>
       <c r="S29" t="n">
         <v>0.2</v>
       </c>
       <c r="T29" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="U29" t="n">
         <v>0.2</v>
       </c>
+      <c r="V29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2534,54 +2532,60 @@
         <v>2012</v>
       </c>
       <c r="E30" t="n">
-        <v>0.6833333333333333</v>
+        <v>0.74</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6383333333333334</v>
+        <v>0.6706060606060605</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2226751315721354</v>
+        <v>0.2211164982819459</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1696014828544953</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5062240663900414</v>
+      </c>
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>15</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N30" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.4</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
       <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
         <v>0.4</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.3</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.2</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2605,55 +2609,61 @@
         <v>2012</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9066666666666667</v>
+        <v>0.8733333333333333</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8955542986425339</v>
+        <v>0.8763815789473685</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1465093221462065</v>
+        <v>0.1500851488270326</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1188784941635189</v>
+        <v>0.382114044373813</v>
       </c>
       <c r="I31" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5857841997159522</v>
+      </c>
+      <c r="K31" t="n">
         <v>8</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
+        <v>7</v>
+      </c>
+      <c r="M31" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L31" t="n">
-        <v>13</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="P31" t="n">
         <v>0.8</v>
       </c>
-      <c r="N31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.84</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.18</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="T31" t="n">
-        <v>0.1866666666666667</v>
+        <v>0.64</v>
       </c>
       <c r="U31" t="n">
-        <v>0.1933333333333334</v>
+        <v>0.28</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.2533333333333334</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.2266666666666667</v>
       </c>
     </row>
     <row r="32">
@@ -2684,48 +2694,24 @@
       <c r="G32" t="n">
         <v>0.6397517261347714</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
         <v>1.163216072620251e-07</v>
       </c>
-      <c r="I32" t="n">
-        <v>16</v>
-      </c>
-      <c r="J32" t="n">
-        <v>9</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N32" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2755,48 +2741,24 @@
       <c r="G33" t="n">
         <v>0.64</v>
       </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16</v>
-      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>9</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2826,48 +2788,24 @@
       <c r="G34" t="n">
         <v>0.633694589138031</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
         <v>0.004945225547999144</v>
       </c>
-      <c r="I34" t="n">
-        <v>16</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2889,56 +2827,32 @@
         <v>2008</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4375</v>
+        <v>0.3819444444444445</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6099316826272843</v>
+        <v>0.6303091767436733</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5970282271938142</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.01037416278161608</v>
-      </c>
-      <c r="I35" t="n">
-        <v>16</v>
-      </c>
+        <v>0.5986371884078633</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>9</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0.007305566231870881</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2968,48 +2882,24 @@
       <c r="G36" t="n">
         <v>0.64</v>
       </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>16</v>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N36" t="n">
-        <v>1</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3039,48 +2929,24 @@
       <c r="G37" t="n">
         <v>0.6399850529731999</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>16</v>
-      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3111,46 +2977,52 @@
         <v>0.6399149582541784</v>
       </c>
       <c r="H38" t="n">
+        <v>1.163216072620251e-07</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J38" t="n">
         <v>5.774910310799749e-07</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>16</v>
       </c>
-      <c r="J38" t="n">
-        <v>8</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M38" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.64</v>
       </c>
       <c r="R38" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2666666666666667</v>
+        <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>0.1777777777777778</v>
+        <v>0.64</v>
       </c>
       <c r="U38" t="n">
-        <v>0.08888888888888889</v>
+        <v>0.3</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="39">
@@ -3173,54 +3045,60 @@
         <v>2009</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4409722222222222</v>
+        <v>0.3715277777777778</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6120833333333334</v>
+        <v>0.63125</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6361520000000001</v>
+        <v>0.637704</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>16</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>9</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0.64</v>
       </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1</v>
-      </c>
       <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
         <v>0.64</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.3</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.2</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3253,46 +3131,52 @@
         <v>0.6338368058204651</v>
       </c>
       <c r="H40" t="n">
+        <v>0.004945225547999144</v>
+      </c>
+      <c r="I40" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J40" t="n">
         <v>0.004833243321627378</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>16</v>
       </c>
-      <c r="J40" t="n">
+      <c r="N40" t="n">
         <v>9</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.7804878048780488</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
       <c r="O40" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="U40" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="41">
@@ -3315,55 +3199,61 @@
         <v>2009</v>
       </c>
       <c r="E41" t="n">
-        <v>0.375</v>
+        <v>0.4097222222222223</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5702398439866471</v>
+        <v>0.5843907852936239</v>
       </c>
       <c r="G41" t="n">
-        <v>0.6164883184918493</v>
+        <v>0.6249975118757277</v>
       </c>
       <c r="H41" t="n">
-        <v>0.001678897141775105</v>
+        <v>0.007305566231870881</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>2008</v>
       </c>
       <c r="J41" t="n">
+        <v>0.001027222136371364</v>
+      </c>
+      <c r="K41" t="n">
         <v>9</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>0.7804878048780488</v>
+        <v>7</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O41" t="n">
-        <v>0.64</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="R41" t="n">
-        <v>0.64</v>
+        <v>0.4375</v>
       </c>
       <c r="S41" t="n">
-        <v>0.3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T41" t="n">
-        <v>0.2</v>
+        <v>0.48</v>
       </c>
       <c r="U41" t="n">
-        <v>0.1</v>
+        <v>0.50625</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.4833333333333334</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0.4604166666666666</v>
       </c>
     </row>
     <row r="42">
@@ -3398,42 +3288,48 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>16</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>9</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
       <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>0.7804878048780488</v>
       </c>
-      <c r="N42" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
         <v>0.64</v>
       </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
         <v>0.64</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.3</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.2</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3466,46 +3362,52 @@
         <v>0.6398924456781397</v>
       </c>
       <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J43" t="n">
         <v>1.447725522269862e-11</v>
       </c>
-      <c r="I43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>5</v>
-      </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M43" t="n">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>0.9375</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>0.75</v>
+        <v>0.7804878048780488</v>
       </c>
       <c r="P43" t="n">
-        <v>0.0625</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.64</v>
       </c>
       <c r="R43" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.2104166666666666</v>
+        <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0.1611111111111111</v>
+        <v>0.64</v>
       </c>
       <c r="U43" t="n">
-        <v>0.1118055555555556</v>
+        <v>0.3</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
@@ -3537,46 +3439,52 @@
         <v>0.3997083474543894</v>
       </c>
       <c r="H44" t="n">
+        <v>5.774910310799749e-07</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J44" t="n">
         <v>9.269796436416404e-06</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>10</v>
       </c>
-      <c r="J44" t="n">
-        <v>12</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M44" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="T44" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U44" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.3</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
@@ -3599,54 +3507,60 @@
         <v>2010</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="F45" t="n">
+        <v>0.4600000000000001</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.399204</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>10</v>
+      </c>
+      <c r="L45" t="n">
+        <v>15</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
         <v>0.4</v>
       </c>
-      <c r="G45" t="n">
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
         <v>0.4</v>
       </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>10</v>
-      </c>
-      <c r="J45" t="n">
-        <v>15</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.2</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3679,46 +3593,52 @@
         <v>0.3964213132858276</v>
       </c>
       <c r="H46" t="n">
+        <v>0.004833243321627378</v>
+      </c>
+      <c r="I46" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J46" t="n">
         <v>0.004498659633100033</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>10</v>
       </c>
-      <c r="J46" t="n">
+      <c r="N46" t="n">
         <v>15</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="N46" t="n">
-        <v>1</v>
-      </c>
       <c r="O46" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="U46" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="47">
@@ -3741,55 +3661,61 @@
         <v>2010</v>
       </c>
       <c r="E47" t="n">
+        <v>0.6266666666666667</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.4834756420050537</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.3985603422282052</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.001027222136371364</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.0005590881125243025</v>
+      </c>
+      <c r="K47" t="n">
+        <v>6</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>10</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P47" t="n">
         <v>0.6</v>
       </c>
-      <c r="F47" t="n">
-        <v>0.4867383107088989</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0.3992378639494475</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.0003971452859503358</v>
-      </c>
-      <c r="I47" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" t="n">
-        <v>6</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3</v>
-      </c>
-      <c r="L47" t="n">
-        <v>9</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.6086956521739131</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.3</v>
-      </c>
       <c r="Q47" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="R47" t="n">
         <v>0.4</v>
       </c>
-      <c r="R47" t="n">
+      <c r="S47" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="T47" t="n">
         <v>0.64</v>
       </c>
-      <c r="S47" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0.32</v>
-      </c>
       <c r="U47" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.3799999999999999</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.3866666666666667</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.3933333333333334</v>
       </c>
     </row>
     <row r="48">
@@ -3824,42 +3750,48 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
         <v>10</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>15</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N48" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" t="n">
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="n">
         <v>0.4</v>
       </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1</v>
-      </c>
       <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
         <v>0.4</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.3</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>0.2</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -3892,46 +3824,52 @@
         <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1.447725522269862e-11</v>
       </c>
       <c r="I49" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
         <v>10</v>
       </c>
-      <c r="J49" t="n">
-        <v>15</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0.5714285714285714</v>
-      </c>
       <c r="N49" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>0.3</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="T49" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="U49" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0.8133333333333334</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.9066666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -3960,49 +3898,55 @@
         <v>0.7188704177323103</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2171061075379025</v>
+        <v>0.217111544717987</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4888998500171703</v>
+        <v>9.269796436416404e-06</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>2010</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0.4889770674245241</v>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M50" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P50" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.37</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.4133333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="U50" t="n">
-        <v>0.4566666666666667</v>
+        <v>0.3</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="51">
@@ -4025,55 +3969,61 @@
         <v>2011</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6733333333333333</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6406762192056309</v>
+        <v>0.6530014430014429</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2633358424813289</v>
+        <v>0.2646404182808575</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06085160778335204</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>0.05537950715775174</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W51" t="n">
         <v>0.1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0.1866666666666667</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0.1433333333333333</v>
       </c>
     </row>
     <row r="52">
@@ -4096,55 +4046,61 @@
         <v>2011</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7733333333333333</v>
+        <v>0.6933333333333334</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7201984126984127</v>
+        <v>0.6685989449147343</v>
       </c>
       <c r="G52" t="n">
-        <v>0.2852432727813721</v>
+        <v>0.2505756318569183</v>
       </c>
       <c r="H52" t="n">
-        <v>0.01487493608146906</v>
+        <v>0.004498659633100033</v>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>2010</v>
       </c>
       <c r="J52" t="n">
-        <v>6</v>
+        <v>0.0225653201341629</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M52" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
         <v>0.4</v>
       </c>
       <c r="R52" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.19</v>
+        <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="U52" t="n">
-        <v>0.13</v>
+        <v>0.3</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
@@ -4167,55 +4123,61 @@
         <v>2011</v>
       </c>
       <c r="E53" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.7733333333333333</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8210081585081584</v>
+        <v>0.7337653522947641</v>
       </c>
       <c r="G53" t="n">
-        <v>0.2202869608750037</v>
+        <v>0.2505812723859815</v>
       </c>
       <c r="H53" t="n">
-        <v>1.713269544996963e-05</v>
+        <v>0.0005590881125243025</v>
       </c>
       <c r="I53" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.6037997265286401</v>
+      </c>
+      <c r="K53" t="n">
         <v>10</v>
       </c>
-      <c r="J53" t="n">
-        <v>6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M53" t="n">
-        <v>0.7692307692307693</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0.625</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>0.4</v>
       </c>
       <c r="R53" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.12</v>
+        <v>1</v>
       </c>
       <c r="T53" t="n">
-        <v>0.08000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="U53" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="54">
@@ -4244,48 +4206,54 @@
         <v>0.4733333333333333</v>
       </c>
       <c r="G54" t="n">
-        <v>0.3350785506919857</v>
+        <v>0.335214681002004</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>10</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>15</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N54" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" t="n">
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
         <v>0.4</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1</v>
-      </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
         <v>0.4</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.3</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>0.2</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4309,55 +4277,61 @@
         <v>2011</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8933333333333333</v>
       </c>
       <c r="F55" t="n">
-        <v>0.780877684407096</v>
+        <v>0.8925685425685426</v>
       </c>
       <c r="G55" t="n">
-        <v>0.282606541385438</v>
+        <v>0.2800503003794367</v>
       </c>
       <c r="H55" t="n">
-        <v>5.530121171447283e-07</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.0001040652623891027</v>
+      </c>
+      <c r="K55" t="n">
         <v>10</v>
       </c>
-      <c r="J55" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M55" t="n">
-        <v>0.7142857142857143</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.16</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="U55" t="n">
-        <v>0.05333333333333334</v>
+        <v>0.3</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
@@ -4380,55 +4354,61 @@
         <v>2012</v>
       </c>
       <c r="E56" t="n">
-        <v>0.82</v>
+        <v>0.8266666666666667</v>
       </c>
       <c r="F56" t="n">
-        <v>0.8052686202686202</v>
+        <v>0.7991558441558442</v>
       </c>
       <c r="G56" t="n">
-        <v>0.24675586501407</v>
+        <v>0.215832514015063</v>
       </c>
       <c r="H56" t="n">
-        <v>0.4980951475015878</v>
+        <v>0.4889770674245241</v>
       </c>
       <c r="I56" t="n">
-        <v>7</v>
+        <v>2011</v>
       </c>
       <c r="J56" t="n">
+        <v>0.4702952922273998</v>
+      </c>
+      <c r="K56" t="n">
+        <v>6</v>
+      </c>
+      <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
+        <v>4</v>
+      </c>
+      <c r="N56" t="n">
         <v>13</v>
       </c>
-      <c r="M56" t="n">
-        <v>0.7368421052631579</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O56" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P56" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="Q56" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S56" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="R56" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.25</v>
-      </c>
       <c r="T56" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.76</v>
       </c>
       <c r="U56" t="n">
-        <v>0.2833333333333333</v>
+        <v>0.32</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.3466666666666667</v>
+      </c>
+      <c r="W56" t="n">
+        <v>0.3733333333333334</v>
       </c>
     </row>
     <row r="57">
@@ -4451,55 +4431,61 @@
         <v>2012</v>
       </c>
       <c r="E57" t="n">
-        <v>0.8066666666666666</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7988220551378445</v>
+        <v>0.8090403091060986</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1772604300135964</v>
+        <v>0.1737830050468269</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4668391189611855</v>
+        <v>0.05537950715775174</v>
       </c>
       <c r="I57" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0.2641110506195494</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L57" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M57" t="n">
-        <v>0.7058823529411765</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.625</v>
       </c>
       <c r="P57" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="R57" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="n">
         <v>0.8</v>
       </c>
-      <c r="S57" t="n">
-        <v>0.3</v>
-      </c>
       <c r="T57" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.52</v>
       </c>
       <c r="U57" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.24</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0.08000000000000002</v>
       </c>
     </row>
     <row r="58">
@@ -4522,55 +4508,61 @@
         <v>2012</v>
       </c>
       <c r="E58" t="n">
-        <v>0.7933333333333334</v>
+        <v>0.7533333333333333</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7715509928667823</v>
+        <v>0.7664160401002506</v>
       </c>
       <c r="G58" t="n">
-        <v>0.1959438323974609</v>
+        <v>0.1917702108621597</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4696164429187775</v>
+        <v>0.0225653201341629</v>
       </c>
       <c r="I58" t="n">
-        <v>6</v>
+        <v>2011</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0.5117895007133484</v>
       </c>
       <c r="K58" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M58" t="n">
-        <v>0.7058823529411765</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="P58" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R58" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="S58" t="n">
-        <v>0.3</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="T58" t="n">
-        <v>0.3333333333333334</v>
+        <v>0.52</v>
       </c>
       <c r="U58" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.34</v>
+      </c>
+      <c r="V58" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0.2466666666666667</v>
       </c>
     </row>
     <row r="59">
@@ -4593,55 +4585,61 @@
         <v>2012</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9133333333333333</v>
+        <v>0.8133333333333332</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9025641025641025</v>
+        <v>0.826547619047619</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1423480244754639</v>
+        <v>0.2431557118724186</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6407988137251898</v>
+        <v>0.6037997265286401</v>
       </c>
       <c r="I59" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.6602153186685421</v>
+      </c>
+      <c r="K59" t="n">
         <v>7</v>
       </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
+        <v>4</v>
+      </c>
+      <c r="M59" t="n">
         <v>3</v>
       </c>
-      <c r="L59" t="n">
-        <v>15</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.8235294117647058</v>
-      </c>
       <c r="N59" t="n">
+        <v>11</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P59" t="n">
         <v>0.7</v>
       </c>
-      <c r="O59" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" t="n">
+      <c r="Q59" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="R59" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.88</v>
-      </c>
       <c r="S59" t="n">
-        <v>0.21</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="T59" t="n">
-        <v>0.24</v>
+        <v>0.72</v>
       </c>
       <c r="U59" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
+      </c>
+      <c r="V59" t="n">
+        <v>0.2933333333333333</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0.2966666666666667</v>
       </c>
     </row>
     <row r="60">
@@ -4664,54 +4662,60 @@
         <v>2012</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5966666666666667</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5267948717948717</v>
+        <v>0.6128787878787879</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3160468795061819</v>
+        <v>0.3115193386773867</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.7126099706744871</v>
+      </c>
+      <c r="K60" t="n">
         <v>10</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>15</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
       <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="N60" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" t="n">
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
         <v>0.4</v>
       </c>
-      <c r="P60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>1</v>
-      </c>
       <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
         <v>0.4</v>
       </c>
-      <c r="S60" t="n">
+      <c r="U60" t="n">
         <v>0.3</v>
       </c>
-      <c r="T60" t="n">
+      <c r="V60" t="n">
         <v>0.2</v>
       </c>
-      <c r="U60" t="n">
+      <c r="W60" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4735,55 +4739,61 @@
         <v>2012</v>
       </c>
       <c r="E61" t="n">
-        <v>0.8533333333333333</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8168440617353662</v>
+        <v>0.8053102453102453</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2222609874122116</v>
+        <v>0.2686751499269823</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01329423575621427</v>
+        <v>0.0001040652623891027</v>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>2011</v>
       </c>
       <c r="J61" t="n">
+        <v>1.824758685317772e-05</v>
+      </c>
+      <c r="K61" t="n">
+        <v>8</v>
+      </c>
+      <c r="L61" t="n">
         <v>2</v>
       </c>
-      <c r="K61" t="n">
-        <v>1</v>
-      </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
+        <v>2</v>
+      </c>
+      <c r="N61" t="n">
         <v>13</v>
       </c>
-      <c r="M61" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.9</v>
-      </c>
       <c r="O61" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8</v>
       </c>
       <c r="P61" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Q61" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S61" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="R61" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.11</v>
-      </c>
       <c r="T61" t="n">
-        <v>0.1066666666666667</v>
+        <v>0.84</v>
       </c>
       <c r="U61" t="n">
-        <v>0.1033333333333333</v>
+        <v>0.18</v>
+      </c>
+      <c r="V61" t="n">
+        <v>0.1866666666666667</v>
+      </c>
+      <c r="W61" t="n">
+        <v>0.1933333333333334</v>
       </c>
     </row>
   </sheetData>
@@ -4819,7 +4829,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.514</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="3">
@@ -4829,7 +4839,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.696</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="4">
@@ -4849,7 +4859,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.615</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="6">
@@ -4859,7 +4869,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="7">
@@ -4869,7 +4879,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.644</v>
+        <v>0.672</v>
       </c>
     </row>
   </sheetData>
@@ -4945,25 +4955,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.585</v>
       </c>
       <c r="D2" t="n">
-        <v>0.658</v>
+        <v>0.606</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="F2" t="n">
-        <v>0.499</v>
+        <v>0.527</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H2" t="n">
-        <v>0.987</v>
+        <v>0.783</v>
       </c>
       <c r="I2" t="n">
-        <v>0.197</v>
+        <v>0.277</v>
       </c>
     </row>
     <row r="3">
@@ -4978,25 +4988,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.708</v>
       </c>
       <c r="D3" t="n">
-        <v>0.741</v>
+        <v>0.648</v>
       </c>
       <c r="E3" t="n">
-        <v>0.92</v>
+        <v>0.909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.639</v>
+        <v>0.519</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08</v>
+        <v>0.091</v>
       </c>
       <c r="H3" t="n">
-        <v>0.613</v>
+        <v>0.739</v>
       </c>
       <c r="I3" t="n">
-        <v>0.187</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="4">
@@ -5014,22 +5024,22 @@
         <v>0.621</v>
       </c>
       <c r="D4" t="n">
-        <v>0.718</v>
+        <v>0.55</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>0.725</v>
       </c>
       <c r="F4" t="n">
-        <v>0.616</v>
+        <v>0.653</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.618</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -5044,25 +5054,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.643</v>
       </c>
       <c r="D5" t="n">
-        <v>0.729</v>
+        <v>0.542</v>
       </c>
       <c r="E5" t="n">
-        <v>0.908</v>
+        <v>0.619</v>
       </c>
       <c r="F5" t="n">
-        <v>0.622</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.092</v>
+        <v>0.381</v>
       </c>
       <c r="H5" t="n">
-        <v>0.613</v>
+        <v>0.439</v>
       </c>
       <c r="I5" t="n">
-        <v>0.197</v>
+        <v>0.393</v>
       </c>
     </row>
     <row r="6">
@@ -5077,25 +5087,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
       <c r="D6" t="n">
-        <v>0.738</v>
+        <v>0.618</v>
       </c>
       <c r="E6" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="F6" t="n">
-        <v>0.708</v>
+        <v>0.588</v>
       </c>
       <c r="G6" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="I6" t="n">
-        <v>0.225</v>
+        <v>0.287</v>
       </c>
     </row>
     <row r="7">
@@ -5110,25 +5120,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.672</v>
       </c>
       <c r="D7" t="n">
-        <v>0.752</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.925</v>
       </c>
       <c r="F7" t="n">
-        <v>0.67</v>
+        <v>0.55</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06</v>
+        <v>0.075</v>
       </c>
       <c r="H7" t="n">
-        <v>0.644</v>
+        <v>0.7</v>
       </c>
       <c r="I7" t="n">
-        <v>0.177</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -5174,7 +5184,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.514</v>
+        <v>0.585</v>
       </c>
     </row>
     <row r="3">
@@ -5184,7 +5194,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.696</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="4">
@@ -5204,7 +5214,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.615</v>
+        <v>0.643</v>
       </c>
     </row>
     <row r="6">
@@ -5214,7 +5224,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="7">
@@ -5224,7 +5234,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.644</v>
+        <v>0.672</v>
       </c>
     </row>
     <row r="8">
@@ -5239,7 +5249,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.537</v>
+        <v>0.554</v>
       </c>
     </row>
     <row r="9">
@@ -5249,7 +5259,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.706</v>
+        <v>0.721</v>
       </c>
     </row>
     <row r="10">
@@ -5259,7 +5269,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.51</v>
+        <v>0.511</v>
       </c>
     </row>
     <row r="11">
@@ -5269,7 +5279,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.636</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="12">
@@ -5279,7 +5289,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.584</v>
+        <v>0.587</v>
       </c>
     </row>
     <row r="13">
@@ -5289,7 +5299,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.613</v>
+        <v>0.589</v>
       </c>
     </row>
   </sheetData>
